--- a/workspaces/btc_daily_14days/macd/macd_histogram_12_26.xlsx
+++ b/workspaces/btc_daily_14days/macd/macd_histogram_12_26.xlsx
@@ -575,46 +575,46 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-11.58434741111906</v>
+        <v>-11.54824922324508</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.533700748128766</v>
+        <v>9.503163163906692</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.593387322082691</v>
+        <v>4.578054660937731</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.725025930434541</v>
+        <v>4.708800428117911</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.737201497497182</v>
+        <v>8.708320101551948</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.037150255001904</v>
+        <v>9.007527406794146</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.402359063271412</v>
+        <v>4.38764636926463</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.935532948736999</v>
+        <v>3.922258540276147</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.6789874917024292</v>
+        <v>-0.6774953348009589</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.024401812809394</v>
+        <v>3.014086033043405</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.736857403365782</v>
+        <v>-1.731774854832238</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.702705515537012</v>
+        <v>-1.697811698349142</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.433885640625007</v>
+        <v>2.42603114958635</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.875017324400439</v>
+        <v>-1.869097871967988</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>19</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15.92761431136658</v>
+        <v>15.87611400521767</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>24.84849577036623</v>
+        <v>24.76868509803871</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>19.19389429798827</v>
+        <v>19.13172562361402</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>14.06209635981583</v>
+        <v>14.01585433975385</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.990010410457067</v>
+        <v>2.979212966039988</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.981068759017987</v>
+        <v>-1.975762362171579</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.204487645987463</v>
+        <v>3.193456483700295</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.737370025469666</v>
+        <v>2.72779258387289</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.676888351054089</v>
+        <v>2.667665995532396</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.825648163761251</v>
+        <v>1.819061073237847</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.896777094274142</v>
+        <v>6.874307044680165</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>17.487926306996</v>
+        <v>17.43151231129779</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>22.34919419973929</v>
+        <v>22.27758637732263</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>22.60510582403793</v>
+        <v>22.53281600362803</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>18</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-13.60454943132108</v>
+        <v>-13.56167903160522</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.56481562499743</v>
+        <v>12.5237240354324</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.056365519337191</v>
+        <v>1.051876596242423</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.746830985489559</v>
+        <v>6.723658998803494</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>11.77064712029868</v>
+        <v>11.73155229873559</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>17.63378369275443</v>
+        <v>17.57614622962569</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.98948524819043</v>
+        <v>11.95014056766598</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.959363060123927</v>
+        <v>5.939350768035204</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3331269990719079</v>
+        <v>0.3313472498779007</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.049231172374704</v>
+        <v>5.032231457973701</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.845083041581105</v>
+        <v>4.828996547040795</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.59308519377414</v>
+        <v>21.52297199270248</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>26.7488056089222</v>
+        <v>26.6624140815256</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>27.00586435892515</v>
+        <v>26.9187809159062</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>25</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4934383202099752</v>
+        <v>-0.4924771964753063</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.105463858261196</v>
+        <v>-2.099588832134309</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.502940699027135</v>
+        <v>-6.48305031386019</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-14.37997748779338</v>
+        <v>-14.33512757173587</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-10.9184503530642</v>
+        <v>-10.88464505286817</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-22.63825382965703</v>
+        <v>-22.56637151230322</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-18.72279236181569</v>
+        <v>-18.66331333176279</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-19.19540203909509</v>
+        <v>-19.13434263898325</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.237471482893532</v>
+        <v>-7.214806476666716</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.082182363146856</v>
+        <v>-4.069856353400681</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.29856707261483</v>
+        <v>-8.272352863147759</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-12.27666778681495</v>
+        <v>-12.23808302092593</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-8.689382105094857</v>
+        <v>-8.662181386753666</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-12.45404970889012</v>
+        <v>-12.41455241742096</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>47</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6980510414921497</v>
+        <v>0.6951338551697148</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.170072606097399</v>
+        <v>-5.154071092144541</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.077297041817346</v>
+        <v>5.059684664684809</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>11.59688214272314</v>
+        <v>11.55760983009716</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.801315673381168</v>
+        <v>6.777796281239212</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.840094206367482</v>
+        <v>2.829973757720239</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.505818767811107</v>
+        <v>-1.501555574414859</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.288635101826564</v>
+        <v>2.280555617125245</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.228129929446197</v>
+        <v>2.220256470403669</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.02063135990295</v>
+        <v>-5.005013773281298</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.227378124017619</v>
+        <v>-5.210730824323178</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.327396144119902</v>
+        <v>-7.304294886329878</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.482632886994274</v>
+        <v>-3.471963679747851</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-9.637043780836144</v>
+        <v>-9.606041779127693</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>57</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.879403232490681</v>
+        <v>-6.857262108482807</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.228587097597213</v>
+        <v>-3.218601188174965</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-15.91131911970704</v>
+        <v>-15.8597760176663</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.494683794152976</v>
+        <v>-3.484936959887612</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.234048600686968</v>
+        <v>1.228372652067954</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.532071046549859</v>
+        <v>1.52602096647027</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.475816302951259</v>
+        <v>8.447081822498923</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.737480598289281</v>
+        <v>2.727697807166045</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.677103346067042</v>
+        <v>2.667531623651385</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.06728722968982481</v>
+        <v>0.06644176128332901</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.379537087178392</v>
+        <v>3.368075538038404</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.862781887027303</v>
+        <v>-1.857194651829097</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.284750768024949</v>
+        <v>-2.277772009870198</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.245479230181623</v>
+        <v>3.234570389592939</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>85</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.90520302609233</v>
+        <v>-1.899107954008031</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.01268393082451524</v>
+        <v>0.01204946355578329</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.148897514545105</v>
+        <v>3.137721864432237</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.103008193087227</v>
+        <v>2.09413584494056</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.097793439364551</v>
+        <v>5.078806414164696</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.396846487733619</v>
+        <v>5.377467979874538</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6002055013341092</v>
+        <v>0.5971107298540375</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.046322438512014</v>
+        <v>-1.043637758810362</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-12.89697092491144</v>
+        <v>-12.85408991364393</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-12.57330295102257</v>
+        <v>-12.53131909865813</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-11.60245348476371</v>
+        <v>-11.56353988067883</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-11.57089275815224</v>
+        <v>-11.53218115448146</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-8.454972270057112</v>
+        <v>-8.426813578887341</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-8.206776760314447</v>
+        <v>-8.179258299777544</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>75</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.826771653543616</v>
+        <v>-1.820688392129455</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.229227974120505</v>
+        <v>3.217442512617424</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.50316447629109</v>
+        <v>5.483371221890181</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.635326195730528</v>
+        <v>5.613860149860628</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.093781387661643</v>
+        <v>1.087833530496276</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.726945721500243</v>
+        <v>2.715975872515202</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.370047549111426</v>
+        <v>-5.352626724363617</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-5.839623768362976</v>
+        <v>-5.820247823420559</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7780682612538072</v>
+        <v>0.7754811832377015</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.420158775705275</v>
+        <v>-5.401126095966369</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.963936848690579</v>
+        <v>-6.93940859699164</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-8.268505543712394</v>
+        <v>-8.239567065127112</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.354526422797029</v>
+        <v>-7.32897491583131</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.430181336374218</v>
+        <v>-4.414552417424602</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10.00656167979002</v>
+        <v>10.07900310551005</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6.313445621348343</v>
+        <v>6.360781615100684</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8.004672456308896</v>
+        <v>8.064845215553973</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.8399633769301857</v>
+        <v>0.8510430609972914</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.344140214879985</v>
+        <v>1.358604480924342</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.616214071138259</v>
+        <v>-4.645855958923235</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.659287337214089</v>
+        <v>-3.684016291152169</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.172168647299323</v>
+        <v>-5.208586630801463</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.191043300931852</v>
+        <v>-4.221393958952945</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-8.177548807579967</v>
+        <v>-8.237949377972008</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-9.429883032236603</v>
+        <v>-9.499875799010233</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-11.48764907472153</v>
+        <v>-11.57246225099955</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-15.04749635078928</v>
+        <v>-15.15738402739682</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-13.16040178356276</v>
+        <v>-13.25665768058249</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>99</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.008589835361029</v>
+        <v>-3.996088812759162</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.632007866405836</v>
+        <v>-6.61108697065832</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.996762733546127</v>
+        <v>-3.985167140590789</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-6.900068854915169</v>
+        <v>-6.879313564917865</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6490353954242494</v>
+        <v>0.6444497091119388</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.958359286297153</v>
+        <v>1.950416473913343</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.873710236448638</v>
+        <v>1.866921891280285</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3937912274232147</v>
+        <v>0.3924891032383471</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.344870280264921</v>
+        <v>1.340764028218409</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.50486737582839</v>
+        <v>1.501189013355521</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.739298829520258</v>
+        <v>-1.73167753487234</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.732057416267992</v>
+        <v>-3.71755835870659</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.141451420386645</v>
+        <v>-3.128920214347119</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.8636851985208907</v>
+        <v>-0.8589968618688246</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>165</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.796468623240415</v>
+        <v>-2.787275980920484</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.015506078993262</v>
+        <v>-4.998667238253887</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-6.018304350489586</v>
+        <v>-5.998671177085967</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-5.88947890079455</v>
+        <v>-5.87067938687543</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.036658210743141</v>
+        <v>-7.014466108856695</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-6.741049363469081</v>
+        <v>-6.718896264900636</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-8.042520416396457</v>
+        <v>-8.014827253854435</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-7.298759717803705</v>
+        <v>-7.273004810344695</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-6.75478880741035</v>
+        <v>-6.730618549155757</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-8.217631646067758</v>
+        <v>-8.187270908638745</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-7.210433879629946</v>
+        <v>-7.182905070304663</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-7.786615298576955</v>
+        <v>-7.756675686210492</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-10.03545050661739</v>
+        <v>-9.99760708303436</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-11.00084819061166</v>
+        <v>-10.96000696287929</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.008001427006093</v>
+        <v>-2.010751344890416</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.119897013707316</v>
+        <v>5.127168202776986</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.812051275747834</v>
+        <v>1.814882704249527</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.486301743126063</v>
+        <v>-0.4865570548942131</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.404949151992483</v>
+        <v>1.4075699195648</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.672791583290142</v>
+        <v>-2.676347981787586</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.704523475172323</v>
+        <v>-4.711444301451571</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.201629613658049</v>
+        <v>-4.208076300786431</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7.670989536660976</v>
+        <v>-7.682453408710863</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-9.013931134811372</v>
+        <v>-9.027829002088524</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-11.17078063347527</v>
+        <v>-11.18796830115595</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-12.11480611419416</v>
+        <v>-12.1335287422345</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-12.25496908590058</v>
+        <v>-12.27402984726186</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-12.49282206862355</v>
+        <v>-12.51211339303435</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>252</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.8716410448693</v>
+        <v>1.864861436068608</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.518449154345085</v>
+        <v>-2.510322261148218</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.914345871049989</v>
+        <v>-2.904628368855882</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.771019337453566</v>
+        <v>-4.75427574808262</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.90079290926748</v>
+        <v>-6.877095601278342</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-7.798468890628158</v>
+        <v>-7.769299241316673</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.501229705473861</v>
+        <v>-5.478792620417018</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.778605388889368</v>
+        <v>-4.758323140810283</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.240351730134009</v>
+        <v>-5.217213307989276</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.504516149276739</v>
+        <v>-4.482309881194645</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.305788916831482</v>
+        <v>-6.27566363402839</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.884921978484059</v>
+        <v>-3.863066757803601</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.510551955610907</v>
+        <v>-3.489670575097712</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.259650778516288</v>
+        <v>-3.239949242821424</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.886123723585726</v>
+        <v>1.885924961988934</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.646090298251849</v>
+        <v>-2.645840980609606</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.503187401971857</v>
+        <v>-4.502745289076891</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-6.932270185916025</v>
+        <v>-6.931566199122315</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-5.280899423084932</v>
+        <v>-5.28037216539655</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-6.083118848644432</v>
+        <v>-6.082441898010515</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-6.171354242844743</v>
+        <v>-6.170634059675677</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-7.00864699644044</v>
+        <v>-7.007833125605124</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.341865265642603</v>
+        <v>-6.341081419186807</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-5.734588549345254</v>
+        <v>-5.73381894212973</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.380513812817611</v>
+        <v>-3.379930359758482</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.13102649878293</v>
+        <v>-3.130466025202871</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.254298579094872</v>
+        <v>-0.2540173394445588</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.836228504513052</v>
+        <v>-1.835797838670025</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>311</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.191187516351455</v>
+        <v>-6.16618231681128</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.980916011698568</v>
+        <v>-2.967855933850132</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.664917474586915</v>
+        <v>-4.643591821406851</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.825022218584692</v>
+        <v>-5.796857639248593</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.789961094184072</v>
+        <v>-3.77167534116154</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.173287153682665</v>
+        <v>-3.154035740115845</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.261156015673436</v>
+        <v>-3.239887929836826</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.699945116818959</v>
+        <v>-4.671750361411007</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.410406538000359</v>
+        <v>-5.37776772916979</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-5.946019815667491</v>
+        <v>-5.909194762263269</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-7.448307289580292</v>
+        <v>-7.403804225361867</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-8.059591726383459</v>
+        <v>-8.012507884736692</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.512066872551841</v>
+        <v>-7.46813227060121</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.261543399779676</v>
+        <v>-7.218410938324922</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>365</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.301082227735229</v>
+        <v>2.291924101031512</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1327280959325989</v>
+        <v>-0.1295390710887858</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.077332564884756</v>
+        <v>-1.066785268082064</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.6745549181557351</v>
+        <v>-0.6626964248934542</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.233806629482373</v>
+        <v>-4.207083094241639</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.468534609049286</v>
+        <v>-1.451309096976871</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.007010877173826</v>
+        <v>-0.9898433565605487</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.753946123190964</v>
+        <v>-1.730975041956761</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.269258050859136</v>
+        <v>-1.246336796072647</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.07354973313123736</v>
+        <v>0.09264401838535008</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.138446013313839</v>
+        <v>0.1599538682821446</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.549392019127133</v>
+        <v>1.564200039326266</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.679203098101922</v>
+        <v>1.691890633860815</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.756067107542073</v>
+        <v>2.763529774356222</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.178972911404941</v>
+        <v>-2.17376619689508</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.905262660192641</v>
+        <v>-1.899604263002942</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5305173736880704</v>
+        <v>0.5324837760607721</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.919322060388502</v>
+        <v>1.919770415346008</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.064408270996076</v>
+        <v>1.066645404562351</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4.830050801706747</v>
+        <v>4.825028254105582</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.851160463686611</v>
+        <v>2.851578580251427</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.905589049110304</v>
+        <v>4.902792103206536</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.526796567566336</v>
+        <v>4.525909186594511</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>6.199255005081959</v>
+        <v>6.195607140800441</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>7.132858374481749</v>
+        <v>7.128537766990071</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>8.116193970384032</v>
+        <v>8.109293164083056</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7.063493445615165</v>
+        <v>7.058123726639806</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>6.681789708222638</v>
+        <v>6.676930232417668</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>292</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.808506813360658</v>
+        <v>-1.792909175059009</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.024357223005516</v>
+        <v>-1.010523587126315</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.422028257470785</v>
+        <v>-1.402500964122474</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.294935191494496</v>
+        <v>-1.272436796035414</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5665216361792531</v>
+        <v>0.5775054530338792</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.926400205937483</v>
+        <v>2.921431458730751</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.245605157145782</v>
+        <v>5.23144694271145</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>6.152692800451476</v>
+        <v>6.134889723008286</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7.811934023866833</v>
+        <v>7.787454945820492</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>7.302323453540353</v>
+        <v>7.282515411777766</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.092445311438532</v>
+        <v>7.077762087460222</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.440163488268908</v>
+        <v>6.427213737956336</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.052862973741277</v>
+        <v>7.034356387285413</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>9.028510850992078</v>
+        <v>8.996406486684975</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.5677861695859434</v>
+        <v>0.5693413205624438</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.996544184388668</v>
+        <v>0.9981810359510348</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.5993282216536215</v>
+        <v>0.604110047144097</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.319512468981401</v>
+        <v>-1.307006747492366</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.233488693673117</v>
+        <v>2.234602889375537</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.124623440442868</v>
+        <v>2.124261186125466</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.036303480016258</v>
+        <v>2.038020088002611</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.849840353709688</v>
+        <v>4.843875397310697</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.431452564324395</v>
+        <v>6.422029208360613</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.462362914516511</v>
+        <v>7.45094119215063</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.432668361303634</v>
+        <v>6.426515736685467</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>9.75660243609444</v>
+        <v>9.739587418621014</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>11.39163802633644</v>
+        <v>11.36851313554501</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>12.05480790905196</v>
+        <v>12.02807053339502</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.591307442501886</v>
+        <v>2.616615944773869</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.487237749495804</v>
+        <v>2.502218330443689</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.2028071336577071</v>
+        <v>-0.2531044882327578</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.149408500436131</v>
+        <v>3.13764162852592</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.000377941237033</v>
+        <v>1.987815523452085</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.639119721197339</v>
+        <v>4.68768496204779</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.574361196660242</v>
+        <v>4.607850327282947</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.837855191023543</v>
+        <v>2.845649047402624</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.781421977483632</v>
+        <v>2.785134221902098</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.80064491403418</v>
+        <v>2.800809902675041</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.446025525772264</v>
+        <v>6.492160474461301</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.633450778397879</v>
+        <v>2.630439735702936</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.90583995624123</v>
+        <v>3.94178685635972</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.861067200157152</v>
+        <v>2.892806889934754</v>
       </c>
     </row>
     <row r="26">
@@ -1612,49 +1612,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.5132403004079933</v>
+        <v>-0.5248136783761836</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.114912923273245</v>
+        <v>-3.153961312352827</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.529583610067903</v>
+        <v>-1.570702034231203</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.379528497262335</v>
+        <v>-3.442335243552996</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.927850702433567</v>
+        <v>-2.977437451939416</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.105656289470325</v>
+        <v>-5.160258169429113</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.928250555867642</v>
+        <v>-2.972598582244487</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.418041407346244</v>
+        <v>-1.449829023068062</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6959787879025185</v>
+        <v>-0.723523786755905</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.4463893412656645</v>
+        <v>0.426351028216132</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.744210949489748</v>
+        <v>-0.7784022961013903</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.2178497353490627</v>
+        <v>-0.2440191387559807</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.125411996556338</v>
+        <v>-3.164273749700889</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.892679977113247</v>
+        <v>-1.91455241742463</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2011724582331453</v>
+        <v>0.1949657257733861</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.781215611735917</v>
+        <v>2.78127245941041</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.38035888118722</v>
+        <v>5.384643128655298</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.504623989842628</v>
+        <v>8.519176994510943</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.768597984351331</v>
+        <v>6.78197785973709</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.078015969971183</v>
+        <v>1.065680024607772</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2043225377202589</v>
+        <v>-0.2281882250634197</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3209874612571681</v>
+        <v>-0.3432467921399009</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.2176741616800584</v>
+        <v>0.1981629602320041</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.42370352551707</v>
+        <v>-2.459191140458472</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.423979148136183</v>
+        <v>-1.459125187667645</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.59149635075952</v>
+        <v>-2.629561307430684</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.416385022134484</v>
+        <v>-2.447406279821372</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.972521128495941</v>
+        <v>-4.004913863207705</v>
       </c>
     </row>
     <row r="28">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.02801</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4094</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2411860679577273</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.02621</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4072~4085</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4072</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.1800968269419272</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.0244</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4053~4066</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4053</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.255366505158328</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.0226</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4035~4048</t>
-        </is>
+      <c r="B9" t="n">
+        <v>4035</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.1960074901704516</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.02079</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4010~4023</t>
-        </is>
+      <c r="B10" t="n">
+        <v>4010</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.1941591752932439</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.01898</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3963~3976</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3963</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.2047059258437756</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.01718</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3906~3919</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3906</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.1076256128866788</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.01537</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3821~3834</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3821</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.0677732184885329</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.01357</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3746~3759</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3746</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.03267747956085998</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.01176</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3651~3663</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3651</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.2957861225577716</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.009957</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3552~3564</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3552</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.1926526860910158</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.008151</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3387~3399</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3387</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.06625385419055618</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.006346</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3182~3193</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3182</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.05902018276528764</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.00454</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2930~2941</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2930</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.09629449158025238</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.002734</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2657~2667</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2657</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.299962504686917</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; -0.0009288</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2346~2356</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2346</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.4776992010124346</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.0008768</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1981~1991</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1981</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.1434275763244273</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.002682</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1664~1673</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1664</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.5848641304774134</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.004488</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1372~1381</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1372</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.090920839818985</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.006294</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1128~1136</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1128</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.203744778381576</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.008099</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>897~900</t>
-        </is>
+      <c r="B26" t="n">
+        <v>897</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.8398950131233605</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.009905</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>697~698</t>
-        </is>
+      <c r="B27" t="n">
+        <v>697</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.231490046552203</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.01171</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>531~531</t>
-        </is>
+      <c r="B28" t="n">
+        <v>531</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.555525898245769</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.01352</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>399~399</t>
-        </is>
+      <c r="B29" t="n">
+        <v>399</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.140646892822602</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.01532</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>305~305</t>
-        </is>
+      <c r="B30" t="n">
+        <v>305</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.018028484144395</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.01713</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>220~220</t>
-        </is>
+      <c r="B31" t="n">
+        <v>220</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-4.766165592937249</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.01893</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>168~168</t>
-        </is>
+      <c r="B32" t="n">
+        <v>168</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-6.064866891638545</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.02074</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>124~124</t>
-        </is>
+      <c r="B33" t="n">
+        <v>124</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-5.719244771822879</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.02254</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>103~103</t>
-        </is>
+      <c r="B34" t="n">
+        <v>103</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-3.949748999821622</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.02435</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-1.302962129733785</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.02801</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>11.79227596550432</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.02621</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>106~106</t>
-        </is>
+      <c r="B7" t="n">
+        <v>106</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>6.940523943940967</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.0244</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>125~125</t>
-        </is>
+      <c r="B8" t="n">
+        <v>125</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>8.306561679790022</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.0226</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>143~143</t>
-        </is>
+      <c r="B9" t="n">
+        <v>143</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>5.548519721748065</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.02079</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>168~168</t>
-        </is>
+      <c r="B10" t="n">
+        <v>168</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4.649418822647164</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.01898</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>215~215</t>
-        </is>
+      <c r="B11" t="n">
+        <v>215</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.785631447231886</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.01718</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>272~272</t>
-        </is>
+      <c r="B12" t="n">
+        <v>272</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.550679326848844</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.01537</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>357~357</t>
-        </is>
+      <c r="B13" t="n">
+        <v>357</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.72785019519619</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.01357</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>432~432</t>
-        </is>
+      <c r="B14" t="n">
+        <v>432</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.2843394575678033</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.01176</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>527~528</t>
-        </is>
+      <c r="B15" t="n">
+        <v>527</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2.052016225244564</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.009957</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>626~627</t>
-        </is>
+      <c r="B16" t="n">
+        <v>626</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.095078426201511</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.008151</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>791~792</t>
-        </is>
+      <c r="B17" t="n">
+        <v>791</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.2843394575678033</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.006346</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>996~998</t>
-        </is>
+      <c r="B18" t="n">
+        <v>996</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.1888291017731021</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.00454</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1248~1250</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1248</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.2265616797900236</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.002734</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1521~1524</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1521</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.5249343832021012</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; -0.0009288</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1832~1835</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1832</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.6133293283843599</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.0008768</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2197~2200</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2197</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.1298019565736084</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.002682</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2514~2518</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2514</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.3885932050392</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.004488</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2806~2810</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2806</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.5361429465444942</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.006294</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3050~3055</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3050</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.4476118062983545</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.008099</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3281~3291</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3281</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.2296887000337406</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.009905</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3481~3493</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3481</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.2460864736597372</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.01171</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3647~3660</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3647</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.225678757368442</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.01352</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3779~3792</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3779</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.120020598690985</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.01532</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3873~3886</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3873</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.07990187536388049</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.01713</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3958~3971</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3958</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.2640534954535809</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.01893</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4010~4023</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4010</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.2532681177716327</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.02074</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4054~4067</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4054</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1743757933872701</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.02254</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4075~4088</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4075</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.09951667000529341</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.02435</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4094</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.02664933501281297</v>

--- a/workspaces/btc_daily_14days/macd/macd_histogram_12_26.xlsx
+++ b/workspaces/btc_daily_14days/macd/macd_histogram_12_26.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MACD Histogram-12-26 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MACD Histogram-12-26 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-11.54824922324508</v>
+        <v>-11.5357762369031</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.503163163906692</v>
+        <v>9.516041219237962</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.578054660937731</v>
+        <v>4.591029365812069</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.708800428117911</v>
+        <v>4.72175041150853</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.708320101551948</v>
+        <v>8.721406487538218</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.007527406794146</v>
+        <v>9.020548808105197</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.38764636926463</v>
+        <v>4.400691780993348</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.922258540276147</v>
+        <v>3.935421350390172</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.6774953348009589</v>
+        <v>-0.6643131881549138</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.014086033043405</v>
+        <v>3.027478569730135</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.731774854832238</v>
+        <v>-1.71832793158368</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.697811698349142</v>
+        <v>-1.684366312348629</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.42603114958635</v>
+        <v>2.439583950606604</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.869097871967988</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>19</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15.87611400521767</v>
+        <v>15.88860803337941</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>24.76868509803871</v>
+        <v>24.78157401930977</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>19.13172562361402</v>
+        <v>19.14470975061968</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>14.01585433975385</v>
+        <v>14.0288097104691</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.979212966039988</v>
+        <v>2.992296024235074</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.975762362171579</v>
+        <v>-1.962746469524056</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.193456483700295</v>
+        <v>3.206501196848521</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.72779258387289</v>
+        <v>2.740954789925219</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.667665995532396</v>
+        <v>2.680848989846211</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.819061073237847</v>
+        <v>1.832453199987036</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.874307044680165</v>
+        <v>6.887755430366077</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>17.43151231129779</v>
+        <v>17.44495995295713</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>22.27758637732263</v>
+        <v>22.29114035491844</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>22.53281600362803</v>
+        <v>22.52238636792988</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>18</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-13.56167903160522</v>
+        <v>-13.54920856887126</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.5237240354324</v>
+        <v>12.53660393655308</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.051876596242423</v>
+        <v>1.064848453145494</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.723658998803494</v>
+        <v>6.736609766030867</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>11.73155229873559</v>
+        <v>11.7446399462714</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>17.57614622962569</v>
+        <v>17.58917145351083</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.95014056766598</v>
+        <v>11.9631888545803</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.939350768035204</v>
+        <v>5.952513993480316</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3313472498779007</v>
+        <v>0.3445293916583836</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.032231457973701</v>
+        <v>5.045624258696613</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.828996547040795</v>
+        <v>4.842444486395898</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.52297199270248</v>
+        <v>21.53642011371618</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>26.6624140815256</v>
+        <v>26.67596832185568</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>26.9187809159062</v>
+        <v>26.90835128020804</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>25</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4924771964753063</v>
+        <v>-0.4799968727224027</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.099588832134309</v>
+        <v>-2.086720027174181</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.48305031386019</v>
+        <v>-6.470083963033595</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-14.33512757173587</v>
+        <v>-14.32219012076917</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-10.88464505286817</v>
+        <v>-10.87157020758543</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-22.56637151230322</v>
+        <v>-22.55336630941468</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-18.66331333176279</v>
+        <v>-18.65027848073184</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-19.13434263898325</v>
+        <v>-19.12118891874366</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.214806476666716</v>
+        <v>-7.201626853693512</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.069856353400681</v>
+        <v>-4.056465932091633</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.272352863147759</v>
+        <v>-8.258907455913018</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-12.23808302092593</v>
+        <v>-12.22463911171702</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-8.662181386753666</v>
+        <v>-8.648629343706702</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-12.41455241742096</v>
+        <v>-12.42498205312275</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>47</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6951338551697148</v>
+        <v>0.707614394350756</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.154071092144541</v>
+        <v>-5.141205380708847</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.059684664684809</v>
+        <v>5.072658260016901</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>11.55760983009716</v>
+        <v>11.57056280890094</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.777796281239212</v>
+        <v>6.790880463869243</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.829973757720239</v>
+        <v>2.842990982084999</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.501555574414859</v>
+        <v>-1.488513805584923</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.280555617125245</v>
+        <v>2.293716880296842</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.220256470403669</v>
+        <v>2.233438705930745</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.005013773281298</v>
+        <v>-4.991623874063592</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.210730824323178</v>
+        <v>-5.197285076296012</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.304294886329878</v>
+        <v>-7.290850528622229</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.471963679747851</v>
+        <v>-3.458411388679551</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-9.606041779127693</v>
+        <v>-9.616471414823913</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>57</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.857262108482807</v>
+        <v>-6.844789069394089</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.218601188174965</v>
+        <v>-3.205735230080627</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-15.8597760176663</v>
+        <v>-15.84681824773891</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.484936959887612</v>
+        <v>-3.471994302260825</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.228372652067954</v>
+        <v>1.241452973149116</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.52602096647027</v>
+        <v>1.539036869068788</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.447081822498923</v>
+        <v>8.460127480312977</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.727697807166045</v>
+        <v>2.740858746428678</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.667531623651385</v>
+        <v>2.680713587403204</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.06644176128332901</v>
+        <v>0.07983255076096185</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.368075538038404</v>
+        <v>3.381522637958874</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.857194651829097</v>
+        <v>-1.843749815828495</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.277772009870198</v>
+        <v>-2.264219746096678</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.234570389592939</v>
+        <v>3.224140753894787</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>85</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.899107954008031</v>
+        <v>-1.886632554431976</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.01204946355578329</v>
+        <v>0.02491635449094787</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.137721864432237</v>
+        <v>3.150691651156897</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.09413584494056</v>
+        <v>2.107080888165626</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.078806414164696</v>
+        <v>5.091888010823475</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.377467979874538</v>
+        <v>5.390485023205279</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.5971107298540375</v>
+        <v>0.6101520181996705</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.043637758810362</v>
+        <v>-1.030479067239142</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-12.85408991364393</v>
+        <v>-12.84091384385692</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-12.53131909865813</v>
+        <v>-12.51793228573123</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-11.56353988067883</v>
+        <v>-11.55009619841977</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-11.53218115448146</v>
+        <v>-11.51873792788043</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-8.426813578887341</v>
+        <v>-8.413261881775242</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-8.179258299777544</v>
+        <v>-8.189687935476236</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>75</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.820688392129455</v>
+        <v>-1.80821498473572</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.217442512617424</v>
+        <v>3.230310315030628</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.483371221890181</v>
+        <v>5.496341358978995</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.613860149860628</v>
+        <v>5.62680631940664</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.087833530496276</v>
+        <v>1.100911479564282</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.715975872515202</v>
+        <v>2.72899043620879</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.352626724363617</v>
+        <v>-5.339589442789325</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-5.820247823420559</v>
+        <v>-5.807092135979104</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7754811832377015</v>
+        <v>0.7886609472298858</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.401126095966369</v>
+        <v>-5.38773818158792</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.93940859699164</v>
+        <v>-6.925964610234224</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-8.239567065127112</v>
+        <v>-8.226123824224608</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.32897491583131</v>
+        <v>-7.315423350877822</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.414552417424602</v>
+        <v>-4.424982053121539</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10.07900310551005</v>
+        <v>9.341361989374555</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6.360781615100684</v>
+        <v>5.682215727335077</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8.064845215553973</v>
+        <v>8.373477505224699</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.8510430609972914</v>
+        <v>1.307962192177371</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.358604480924342</v>
+        <v>1.800022980781534</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.645855958923235</v>
+        <v>-4.074287135477519</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.684016291152169</v>
+        <v>-3.130327292578961</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.208586630801463</v>
+        <v>-4.626482062433347</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.221393958952945</v>
+        <v>-3.658902530730792</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-8.237949377972008</v>
+        <v>-7.598099134776021</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-9.499875799010233</v>
+        <v>-8.834782531776824</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-11.57246225099955</v>
+        <v>-10.86364449516757</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-15.15738402739682</v>
+        <v>-14.37868789645754</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-13.25665768058249</v>
+        <v>-12.09508514590673</v>
       </c>
     </row>
     <row r="15">
@@ -1040,257 +1040,257 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.996088812759162</v>
+        <v>-3.489589331333505</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.61108697065832</v>
+        <v>-6.113634522753969</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.985167140590789</v>
+        <v>-4.474772291738084</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-6.879313564917865</v>
+        <v>-7.399153646624654</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6444497091119388</v>
+        <v>0.2047417306348507</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.950416473913343</v>
+        <v>1.520525910400835</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.866921891280285</v>
+        <v>1.437033914167941</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3924891032383471</v>
+        <v>-0.04723429901410015</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.340764028218409</v>
+        <v>0.9109980229469059</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.501189013355521</v>
+        <v>1.081843690493365</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.73167753487234</v>
+        <v>-2.18103925180786</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.71755835870659</v>
+        <v>-4.187077488482224</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.128920214347119</v>
+        <v>-3.588323504496692</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.8589968618688246</v>
+        <v>-1.322941236795998</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.009054</t>
+          <t>X ≈ -0.009053</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>165</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.787275980920484</v>
+        <v>-2.774046660320316</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.998667238253887</v>
+        <v>-4.98441249810918</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.998671177085967</v>
+        <v>-5.98408234525467</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-5.87067938687543</v>
+        <v>-5.856182696725462</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.014466108856695</v>
+        <v>-6.99955116882937</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-6.718896264900636</v>
+        <v>-6.704047466039945</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-8.014827253854435</v>
+        <v>-7.999489576991699</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-7.273004810344695</v>
+        <v>-7.257708768324889</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-6.730618549155757</v>
+        <v>-6.715431514117022</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-8.187270908638745</v>
+        <v>-8.17135743140787</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-7.182905070304663</v>
+        <v>-7.16716989498245</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-7.756675686210492</v>
+        <v>-7.740739356752378</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-9.99760708303436</v>
+        <v>-9.980903112955318</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-10.96000696287929</v>
+        <v>-10.97043659857744</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.007248</t>
+          <t>X ≈ -0.007247</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.010751344890416</v>
+        <v>-2.241709424421636</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.127168202776986</v>
+        <v>4.851862192542626</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.814882704249527</v>
+        <v>1.554744544938899</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4865570548942131</v>
+        <v>-0.7343171773244634</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.4075699195648</v>
+        <v>1.147425024602065</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.676347981787586</v>
+        <v>-2.914003828462896</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.711444301451571</v>
+        <v>-4.938938391331256</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.208076300786431</v>
+        <v>-4.440344801256408</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7.682453408710863</v>
+        <v>-7.897103213665986</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-9.027829002088524</v>
+        <v>-9.239402552714502</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-11.18796830115595</v>
+        <v>-10.90421787939037</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-12.1335287422345</v>
+        <v>-12.3299003670884</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-12.27402984726186</v>
+        <v>-12.75679168232723</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-12.51211339303435</v>
+        <v>-12.73566166477324</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.005443</t>
+          <t>X ≈ -0.005442</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>252</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.864861436068608</v>
+        <v>1.876767397671451</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.510322261148218</v>
+        <v>-2.10133296714698</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.904628368855882</v>
+        <v>-2.89073782814804</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.75427574808262</v>
+        <v>-4.739774461195807</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.877095601278342</v>
+        <v>-6.86183049617717</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-7.769299241316673</v>
+        <v>-7.753604558721136</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.478792620417018</v>
+        <v>-5.463686631111294</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.758323140810283</v>
+        <v>-4.743298290780515</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.217213307989276</v>
+        <v>-5.201911076112324</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.482309881194645</v>
+        <v>-4.466886001897933</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.27566363402839</v>
+        <v>-6.656043734576173</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.863066757803601</v>
+        <v>-3.847627630839852</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.489670575097712</v>
+        <v>-3.476114528746109</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.239949242821424</v>
+        <v>-2.853553481694185</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.003637</t>
+          <t>X ≈ -0.003636</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.885924961988934</v>
+        <v>2.096831460402136</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.645840980609606</v>
+        <v>-2.80982247945704</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.502745289076891</v>
+        <v>-4.304940490823441</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-6.931566199122315</v>
+        <v>-6.742139329152756</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-5.28037216539655</v>
+        <v>-5.083355809104013</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-6.082441898010515</v>
+        <v>-5.888900055200551</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-6.170634059675677</v>
+        <v>-5.976844836713347</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-7.007833125605124</v>
+        <v>-6.814862367594323</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.341081419186807</v>
+        <v>-6.145453322826832</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-5.73381894212973</v>
+        <v>-5.532604236988448</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.379930359758482</v>
+        <v>-3.169877434294072</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.130466025202871</v>
+        <v>-3.137563437066603</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.2540173394445588</v>
+        <v>-0.03307064452583575</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.835797838670025</v>
+        <v>-2.013217347240406</v>
       </c>
     </row>
     <row r="20">
@@ -1303,202 +1303,202 @@
         <v>311</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.16618231681128</v>
+        <v>-6.151262475451524</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.967855933850132</v>
+        <v>-2.953731919805378</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.643591821406851</v>
+        <v>-4.628538914259671</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.796857639248593</v>
+        <v>-5.781141977629993</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.77167534116154</v>
+        <v>-3.756803296575882</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.154035740115845</v>
+        <v>-3.139126232820381</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.239887929836826</v>
+        <v>-3.224744485774679</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.671750361411007</v>
+        <v>-4.655791203471757</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.37776772916979</v>
+        <v>-5.36133688644901</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-5.909194762263269</v>
+        <v>-5.89212910323964</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-7.403804225361867</v>
+        <v>-7.38590802956039</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-8.012507884736692</v>
+        <v>-7.999055596016582</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.46813227060121</v>
+        <v>-7.454576224249607</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.218410938324922</v>
+        <v>-7.228840574023074</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -2.6e-05</t>
+          <t>X ≈ -2.555e-05</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>365</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.291924101031512</v>
+        <v>2.303411532010045</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1295390710887858</v>
+        <v>-0.1164283742925534</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.066785268082064</v>
+        <v>-1.052834804231445</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.6626964248934542</v>
+        <v>-0.6486319820890429</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.207083094241639</v>
+        <v>-4.191393139125132</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.451309096976871</v>
+        <v>-1.43662148077668</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9898433565605487</v>
+        <v>-0.9751258260402906</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.730975041956761</v>
+        <v>-1.715551272851918</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.246336796072647</v>
+        <v>-1.230887066651711</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.09264401838535008</v>
+        <v>0.1079308979973064</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1599538682821446</v>
+        <v>0.1755478136902795</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.564200039326266</v>
+        <v>1.577652328046376</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.691890633860815</v>
+        <v>1.705446680212418</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.763529774356222</v>
+        <v>2.75310013865807</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001779</t>
+          <t>X ≈ 0.00178</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>317</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.17376619689508</v>
+        <v>-2.159934672859123</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.899604263002942</v>
+        <v>-1.885250868165386</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5324837760607721</v>
+        <v>0.5459680878213433</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.919770415346008</v>
+        <v>1.932839211908245</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.066645404562351</v>
+        <v>1.080339500821346</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4.825028254105582</v>
+        <v>4.836736184496971</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.851578580251427</v>
+        <v>2.864778163663964</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.902792103206536</v>
+        <v>4.915266392841737</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.525909186594511</v>
+        <v>4.538929225496631</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>6.195607140800441</v>
+        <v>6.208115277003486</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>7.128537766990071</v>
+        <v>6.948136771428047</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>8.109293164083056</v>
+        <v>8.122745452803166</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7.058123726639806</v>
+        <v>7.071679772991409</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>6.676930232417668</v>
+        <v>6.666500596719516</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.003585</t>
+          <t>X ≈ 0.003586</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>292</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.792909175059009</v>
+        <v>-1.778895786527059</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.010523587126315</v>
+        <v>-0.9963017635499227</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.402500964122474</v>
+        <v>-1.387531129991309</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.272436796035414</v>
+        <v>-1.257142238193452</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5775054530338792</v>
+        <v>0.591682336273017</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.921431458730751</v>
+        <v>2.933800757691252</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.23144694271145</v>
+        <v>5.242843956766244</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>6.134889723008286</v>
+        <v>6.146020252780303</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7.787454945820492</v>
+        <v>7.797885953294866</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>7.282515411777766</v>
+        <v>7.2936948554661</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.077762087460222</v>
+        <v>7.09121938117044</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.427213737956336</v>
+        <v>6.440666026676446</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.034356387285413</v>
+        <v>7.047912433637016</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>8.996406486684975</v>
+        <v>8.985976850986823</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>244</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.5693413205624438</v>
+        <v>0.3638446404403055</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.9981810359510348</v>
+        <v>1.011454305968208</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.604110047144097</v>
+        <v>0.6184441296430023</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.307006747492366</v>
+        <v>-1.290379371059657</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.234602889375537</v>
+        <v>2.248029625438484</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.124261186125466</v>
+        <v>2.137219379105616</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.038020088002611</v>
+        <v>2.051655152804258</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.843875397310697</v>
+        <v>4.855383906658922</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.422029208360613</v>
+        <v>6.432565174153247</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.45094119215063</v>
+        <v>7.219877464956468</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.426515736685467</v>
+        <v>6.439973030395684</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>9.739587418621014</v>
+        <v>9.753039707341124</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>11.36851313554501</v>
+        <v>11.38206918189661</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>12.02807053339502</v>
+        <v>12.01764089769687</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>231</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.616615944773869</v>
+        <v>2.629138234449492</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.502218330443689</v>
+        <v>2.27539579319545</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.2531044882327578</v>
+        <v>-0.4855640004358364</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.13764162852592</v>
+        <v>2.90016008251974</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.987815523452085</v>
+        <v>1.752688261981049</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.68768496204779</v>
+        <v>4.456627699535055</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.607850327282947</v>
+        <v>4.618670018969873</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.845649047402624</v>
+        <v>2.858232727802623</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.785134221902098</v>
+        <v>2.798045169572099</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.800809902675041</v>
+        <v>2.814215030327873</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.492160474461301</v>
+        <v>6.505617768171518</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.630439735702936</v>
+        <v>2.643892024423046</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.94178685635972</v>
+        <v>3.955342902711322</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.892806889934754</v>
+        <v>2.882377254236602</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>200</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.5248136783761836</v>
+        <v>-0.5122913887005609</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.153961312352827</v>
+        <v>-3.141051502776776</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.570702034231203</v>
+        <v>-1.557694902813601</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.442335243552996</v>
+        <v>-3.429356101154532</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.977437451939416</v>
+        <v>-2.964326647564477</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.160258169429113</v>
+        <v>-5.147215273134748</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.972598582244487</v>
+        <v>-3.243343970509827</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.449829023068062</v>
+        <v>-1.431050359939846</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.723523786755905</v>
+        <v>-0.998743756041705</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.426351028216132</v>
+        <v>0.4397561558689631</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.7784022961013903</v>
+        <v>-0.7649450023911726</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.2440191387559807</v>
+        <v>-0.2305668500358706</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.164273749700889</v>
+        <v>-3.150717703349287</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.91455241742463</v>
+        <v>-1.924982053122783</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>166</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1949657257733861</v>
+        <v>0.2074880154490089</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.78127245941041</v>
+        <v>2.794182268986461</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.384643128655298</v>
+        <v>5.397650260072901</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.519176994510943</v>
+        <v>8.532156136909407</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.78197785973709</v>
+        <v>6.795088664112029</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.065680024607772</v>
+        <v>1.078722920902138</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2281882250634197</v>
+        <v>-0.2151219707629437</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3432467921399009</v>
+        <v>-0.6821906145496826</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.1981629602320041</v>
+        <v>0.2113616991867673</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.459191140458472</v>
+        <v>-2.445786012805641</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.459125187667645</v>
+        <v>-1.445667893957427</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.629561307430684</v>
+        <v>-2.616109018710574</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.447406279821372</v>
+        <v>-2.433850233469769</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-4.004913863207705</v>
+        <v>-4.015343498905857</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>132</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.809591982820322</v>
+        <v>2.822114272495945</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.713169885007602</v>
+        <v>2.726079694583653</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.10617996628983</v>
+        <v>6.119187097707432</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.509160371624603</v>
+        <v>8.522139514023067</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7.970739156552384</v>
+        <v>7.983849960927323</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.23787806396502</v>
+        <v>5.250920960259386</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.395568589117026</v>
+        <v>4.408634843417502</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.928385190335526</v>
+        <v>3.941566199630763</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.435644998877059</v>
+        <v>-1.422446259922296</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7706186687535777</v>
+        <v>-0.7572135411007466</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-1.719490456936661</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.456140350877156</v>
+        <v>-2.442688062157046</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.9114838260566884</v>
+        <v>0.9250398724082913</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.869097871970062</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>94</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.14485955213042</v>
+        <v>8.157381841806043</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>11.85243487533644</v>
+        <v>11.86534468491249</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>12.52139595597386</v>
+        <v>12.53440308739146</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.52398951411327</v>
+        <v>10.53696865651174</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>12.11322787350919</v>
+        <v>12.12633867788413</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.219180449522725</v>
+        <v>9.23222334581709</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.134446732250446</v>
+        <v>9.147512986550922</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.411944184532771</v>
+        <v>4.425125193828009</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.223284723882358</v>
+        <v>2.236483462837121</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.564648900556591</v>
+        <v>4.578054028209422</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.296065789004942</v>
+        <v>3.30952308271516</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.330448946350337</v>
+        <v>3.343901235070447</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.037853909873576</v>
+        <v>5.051409956225179</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>5.287575242149863</v>
+        <v>5.277145606451711</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>85</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.683032268025357</v>
+        <v>8.69555455770098</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.365576302119877</v>
+        <v>2.378486111695928</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.676589948464475</v>
+        <v>6.689597079882077</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.983313669307279</v>
+        <v>7.996292811705743</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.739010101293907</v>
+        <v>2.752120905668846</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.859981450774285</v>
+        <v>1.87302434706865</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.951718321737296</v>
+        <v>2.964784576037772</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.952946801479385</v>
+        <v>5.966145540434148</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.279292204686747</v>
+        <v>6.292697332339579</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.427480056839826</v>
+        <v>8.440937350550044</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.638333802420448</v>
+        <v>9.651786091140558</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.041608603240284</v>
+        <v>8.055164649591887</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.938388759045985</v>
+        <v>5.927959123347833</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>52</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.5703613971330483</v>
+        <v>-0.5578391074574256</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.664218836056541</v>
+        <v>1.677128645632592</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.961657821767638</v>
+        <v>8.97466495318524</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>12.93806480052896</v>
+        <v>12.95104394292742</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.47656666237991</v>
+        <v>10.48967746675485</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>18.46631629240323</v>
+        <v>18.4793591886976</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.45850565205405</v>
+        <v>16.47157190635453</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.1451684071187</v>
+        <v>12.15834941641393</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>14.00724544401331</v>
+        <v>14.02044418296808</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>17.00327410513923</v>
+        <v>17.01667923279206</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.95236693466774</v>
+        <v>12.96582422837795</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>16.83290393816712</v>
+        <v>16.84635622688723</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.56649548106834</v>
+        <v>12.58005152741994</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.046986044113858</v>
+        <v>7.036556408415706</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>44</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.038892865664522</v>
+        <v>-7.026370575988899</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>11.8040789759167</v>
+        <v>11.81698878549275</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>15.95466481477463</v>
+        <v>15.96767194619223</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.72128158374575</v>
+        <v>4.734260726144214</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.635321449508218</v>
+        <v>-2.622210645133279</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.480302306389241</v>
+        <v>4.493345202683606</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.668295861844285</v>
+        <v>6.681362116144761</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.201112463062721</v>
+        <v>6.214293472357959</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.412839849607721</v>
+        <v>8.426038588562484</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.835441937307067</v>
+        <v>9.848847064959898</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.630688612989516</v>
+        <v>9.644145906699734</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.846889952153141</v>
+        <v>2.860342240873251</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.426635341208204</v>
+        <v>2.440191387559807</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4036294007572181</v>
+        <v>0.393199765059066</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>21</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-14.39820022497188</v>
+        <v>-14.38567793529626</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-11.24786907603134</v>
+        <v>-11.23495926645528</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.64273778262797</v>
+        <v>-11.62973065121037</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.773229635693852</v>
+        <v>2.786208778092316</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.996713182526413</v>
+        <v>7.009823986901353</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-2.229654403567416</v>
+        <v>-2.216611507273051</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-2.314388120839794</v>
+        <v>-2.301321866539318</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.78157151962116</v>
+        <v>-2.768390510325922</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.681238118005993</v>
+        <v>6.694436856960756</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>15.15016913247001</v>
+        <v>15.16362642618023</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.18455228981537</v>
+        <v>15.19800457853548</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.4785833931562848</v>
+        <v>0.4921394395078877</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>19</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-15.65133305705208</v>
+        <v>-15.63881076737646</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.736590880542657</v>
+        <v>-6.723681070966606</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-12.39461748187605</v>
+        <v>-12.38161035045844</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.525109334941973</v>
+        <v>3.538088477340438</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.276469774867032</v>
+        <v>-2.263358970492092</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.284130057585465</v>
+        <v>3.29717295387983</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-2.063761554423692</v>
+        <v>-2.050695300123216</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.732212941531657</v>
+        <v>2.745393950826895</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.671213055349355</v>
+        <v>2.684411794304118</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.084245765058263</v>
+        <v>7.097650892711094</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-3.646823348732958</v>
+        <v>-3.633366055022741</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.913875598086193</v>
+        <v>6.927327886806303</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-4.032694802332472</v>
+        <v>-4.019138755980869</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-3.782973470056184</v>
+        <v>-3.793403105754336</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MACD Histogram-12-26 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MACD Histogram-12-26 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2411860679577273</v>
+        <v>-0.2413834112549011</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.06214783185908601</v>
+        <v>-0.06239674254144489</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2246065837415898</v>
+        <v>-0.2248179798583294</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3735261426409053</v>
+        <v>-0.3737007399171119</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3382217663495553</v>
+        <v>-0.3384077034356068</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2712601243540576</v>
+        <v>-0.2714610366534416</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2208220916482446</v>
+        <v>-0.2210358272088442</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.235694632280925</v>
+        <v>-0.2359071438996807</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2101058799493742</v>
+        <v>-0.2103250478011418</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2171335984309835</v>
+        <v>-0.2173553347384782</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1397642682761813</v>
+        <v>-0.1400060077596805</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1649175762559878</v>
+        <v>-0.1651531326817164</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.03423711966426168</v>
+        <v>-0.03450676584928658</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.01494323325263736</v>
+        <v>-0.01472564286634537</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1800968269419272</v>
+        <v>-0.1803776066479088</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1138268205395576</v>
+        <v>-0.1141339473435963</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.250554164140155</v>
+        <v>-0.250830413348325</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.4009846850173133</v>
+        <v>-0.4012234321172912</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3870979748696541</v>
+        <v>-0.3873436013490448</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3213910982453285</v>
+        <v>-0.3216511217466618</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2457204968889428</v>
+        <v>-0.2459997376877183</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2581590158261875</v>
+        <v>-0.2584382577897699</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2075806913426206</v>
+        <v>-0.2078728653587731</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2345910718819724</v>
+        <v>-0.2348820585043256</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1311630322977351</v>
+        <v>-0.1314808218220165</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1566357317849523</v>
+        <v>-0.1569472181340359</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.04752933526435044</v>
+        <v>-0.04787037885247969</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.004925698367628684</v>
+        <v>-0.004653057296579277</v>
       </c>
     </row>
     <row r="8">
@@ -2318,101 +2318,101 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.255366505158328</v>
+        <v>-0.2556885901606094</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2304731877867781</v>
+        <v>-0.2308133877398433</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3414160728416888</v>
+        <v>-0.341732056938703</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.4685691758810222</v>
+        <v>-0.4688530891743028</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.4028788551749258</v>
+        <v>-0.403183056920362</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3136355951575993</v>
+        <v>-0.3139597523318187</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2618429648463021</v>
+        <v>-0.2621806744800566</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2721568150845783</v>
+        <v>-0.2724956006379742</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2210595186435427</v>
+        <v>-0.2214115223022546</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2442183580298334</v>
+        <v>-0.2445710989363334</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1640038740106888</v>
+        <v>-0.1643780810207218</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2390869562652327</v>
+        <v>-0.2394425896808485</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1521869218765204</v>
+        <v>-0.152567271783326</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1105800512760666</v>
+        <v>-0.1102311897779131</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.0226</t>
+          <t>X &gt; -0.02259</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4035</v>
+        <v>4036</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1960074901704516</v>
+        <v>-0.1964013355479324</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2873692348792005</v>
+        <v>-0.2877542975112277</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3476315048227292</v>
+        <v>-0.3480052108488891</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.500653465136125</v>
+        <v>-0.5009884537416198</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4570101465678391</v>
+        <v>-0.4573606619890995</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3934413133350745</v>
+        <v>-0.3938052334282389</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3163202148054651</v>
+        <v>-0.3167041262945105</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2998661425929185</v>
+        <v>-0.3002582796999462</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.223523786755905</v>
+        <v>-0.2239355402535068</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2677564241235331</v>
+        <v>-0.2681646362102086</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1862774818369317</v>
+        <v>-0.186707814968571</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.336166773137947</v>
+        <v>-0.3365599159100725</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2718059598099103</v>
+        <v>-0.2722188180384109</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2311571262226124</v>
+        <v>-0.2307303187322631</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1941591752932439</v>
+        <v>-0.1946337243713288</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2760711077142659</v>
+        <v>-0.2765415966282632</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3093807641180035</v>
+        <v>-0.3098471533059808</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4144036265663047</v>
+        <v>-0.4148428437501863</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3919999538851613</v>
+        <v>-0.3924503556714996</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2552060876557221</v>
+        <v>-0.2556877996462248</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2019374646997534</v>
+        <v>-0.2024335307171157</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1824442192987163</v>
+        <v>-0.1829500608078689</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1799372363200504</v>
+        <v>-0.1804445697135009</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2440525592277893</v>
+        <v>-0.2445526859740994</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1358655405569351</v>
+        <v>-0.1363949276527876</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2619653002714415</v>
+        <v>-0.2624631869409413</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.2194968860758522</v>
+        <v>-0.2200098269783979</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1552007964769757</v>
+        <v>-0.1547252593057422</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3963</v>
+        <v>3964</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2047059258437756</v>
+        <v>-0.2053314190181297</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2182194803440396</v>
+        <v>-0.2188626869784684</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3730562814416842</v>
+        <v>-0.3736659611834128</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5563881414447209</v>
+        <v>-0.5569503275227845</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4770316023966146</v>
+        <v>-0.4776210288597937</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2917954019965379</v>
+        <v>-0.2924279365638327</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1865243808853094</v>
+        <v>-0.1871848493551482</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.2116546639900889</v>
+        <v>-0.212315183469812</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.2084028190139762</v>
+        <v>-0.2090652846366226</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1875889768254382</v>
+        <v>-0.1882680376793928</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.07567914935405895</v>
+        <v>-0.07638941882679973</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1784453682641853</v>
+        <v>-0.179129633696995</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1809235983386372</v>
+        <v>-0.1816130375233129</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.04311663645059127</v>
+        <v>-0.04254007532255599</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3906</v>
+        <v>3907</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1076256128866788</v>
+        <v>-0.1084670509425152</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1744351082635589</v>
+        <v>-0.1752866094364052</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.147059603263294</v>
+        <v>-0.1479250652700159</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5136520219743588</v>
+        <v>-0.5144221712494144</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5019184540362573</v>
+        <v>-0.5027009413539147</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3183226761907605</v>
+        <v>-0.319147540843602</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3125140259423773</v>
+        <v>-0.3133422086566853</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.254548440450904</v>
+        <v>-0.2553996252420774</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.2503711403739146</v>
+        <v>-0.2512248433021682</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1912960306073686</v>
+        <v>-0.192179410482332</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1259336340395123</v>
+        <v>-0.1268375855114101</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1539474908542502</v>
+        <v>-0.1548441588104978</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1503244279706593</v>
+        <v>-0.151229474075997</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.0909477067231208</v>
+        <v>-0.09019833159728563</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3821</v>
+        <v>3822</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.0677732184885329</v>
+        <v>-0.06892124565821689</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1785835480972722</v>
+        <v>-0.1797390563055359</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2201311616914907</v>
+        <v>-0.221285196326086</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5716635290897045</v>
+        <v>-0.5727235213410538</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6260643880318355</v>
+        <v>-0.6271227260046359</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4450283044989405</v>
+        <v>-0.4461278568938738</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3327490702351596</v>
+        <v>-0.3338804109808038</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2369947654808442</v>
+        <v>-0.2381621180286402</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.03000470252793264</v>
+        <v>0.02876562374314062</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.0832137733141991</v>
+        <v>0.08194120552921191</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1285014695889544</v>
+        <v>0.1272118603539028</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.09916684084119254</v>
+        <v>0.09788503280930883</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.03379009122009791</v>
+        <v>0.03251535969020836</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.08898068909201839</v>
+        <v>0.08993160464805072</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3746</v>
+        <v>3747</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.03267747956085998</v>
+        <v>-0.03410751989605387</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2465765952285111</v>
+        <v>-0.2479946482057898</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3343230140055837</v>
+        <v>-0.3357292827012799</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.6955061014125263</v>
+        <v>-0.6968133900509841</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6603789486003393</v>
+        <v>-0.6617110807998543</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5083158948022017</v>
+        <v>-0.5096810653226669</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2322443120772135</v>
+        <v>-0.2336860748757559</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1252104677377872</v>
+        <v>-0.1266943434499694</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.01507925243363673</v>
+        <v>0.01355554921377689</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1930176948828262</v>
+        <v>0.1914223782097011</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.270010614007937</v>
+        <v>0.2683883309421375</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2661196019057002</v>
+        <v>0.2644985007243221</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1812026314039983</v>
+        <v>0.1795917950498591</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.1791475291851157</v>
+        <v>0.1803021742591469</v>
       </c>
     </row>
     <row r="15">
@@ -2682,257 +2682,257 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2957861225577716</v>
+        <v>-0.2832638328821488</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4185018294057983</v>
+        <v>-0.4055920198297471</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5528716258401971</v>
+        <v>-0.5671794356954791</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7357477257425558</v>
+        <v>-0.7500909877156801</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7129134393713201</v>
+        <v>-0.7271325065459919</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4006559917368833</v>
+        <v>-0.4149504382528022</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.142428278658393</v>
+        <v>-0.1567068425148719</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.007060344502974658</v>
+        <v>-0.007110943794785385</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1253134225464123</v>
+        <v>0.1111523803794299</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4123937211554036</v>
+        <v>0.3984315800616542</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5242256809037826</v>
+        <v>0.5103082141431585</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5741626794258323</v>
+        <v>0.5602327118480233</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5803167734434567</v>
+        <v>0.5664830635638936</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5287507871768753</v>
+        <v>0.5065247961923163</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.009957</t>
+          <t>X &gt; -0.009956</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3552</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1926526860910158</v>
+        <v>-0.1948010235217268</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.2459044394891308</v>
+        <v>-0.2481066129359988</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4572079839594778</v>
+        <v>-0.4593685967618697</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5645165832655437</v>
+        <v>-0.5666427499417281</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.7507453514489768</v>
+        <v>-0.7528430007024483</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4661841939044962</v>
+        <v>-0.4683504050793985</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1984321263002613</v>
+        <v>-0.2006782935719968</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.003682180022586579</v>
+        <v>-0.006003936809570121</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.09143684316534717</v>
+        <v>0.08908456704282486</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3820472307478084</v>
+        <v>0.3795761783661789</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5871013617488927</v>
+        <v>0.5845627331924845</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6937799043062114</v>
+        <v>0.6912114279607451</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6836992232720789</v>
+        <v>0.6811145510835814</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5674295645573721</v>
+        <v>0.55699992885922</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.008151</t>
+          <t>X &gt; -0.00815</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3387</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.06625385419055618</v>
+        <v>-0.06915132465199747</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.01437037931901841</v>
+        <v>-0.01737426246255325</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1872518496619051</v>
+        <v>-0.1902284230089037</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3060232668806435</v>
+        <v>-0.3089592272906145</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4456039505123712</v>
+        <v>-0.4485303795802267</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1615790885858246</v>
+        <v>-0.1645741975038177</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.182348858655871</v>
+        <v>0.1792460825024733</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3504477975396014</v>
+        <v>0.3472677777460902</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4237778941641679</v>
+        <v>0.4205711786139474</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7995073703990556</v>
+        <v>0.7961407032001659</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9656224899711674</v>
+        <v>0.9621936406766451</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.105449574349088</v>
+        <v>1.101979623850227</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.204046297538554</v>
+        <v>1.200521966072195</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.128996445876254</v>
+        <v>1.118566810178102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.006346</t>
+          <t>X &gt; -0.006345</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.05902018276528764</v>
+        <v>0.07154247244091039</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.3456134369336255</v>
+        <v>-0.3327036273575743</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3162391480754323</v>
+        <v>-0.3032320166578302</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2943923974454563</v>
+        <v>-0.2814132550469921</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5649944732546217</v>
+        <v>-0.5518836688796824</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0004346207499352772</v>
+        <v>0.01347751704430067</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4976309447093072</v>
+        <v>0.5106971990097833</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6441302111652547</v>
+        <v>0.6573112204604925</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.9460209542173956</v>
+        <v>0.9592196931721588</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.432632435251335</v>
+        <v>1.446037562904166</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.748616239870934</v>
+        <v>1.730656631287715</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.958369296190583</v>
+        <v>1.971821584910693</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.072369870663657</v>
+        <v>2.104390753110948</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.007823446811727</v>
+        <v>2.015759851938547</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.00454</t>
+          <t>X &gt; -0.004539</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.09629449158025238</v>
+        <v>-0.08377220190462964</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1594337018817171</v>
+        <v>-0.1805374977478422</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.09362000690250483</v>
+        <v>-0.0806128754849027</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.08918801359910589</v>
+        <v>0.1021671559975701</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.02211069023005052</v>
+        <v>-0.008999885855111245</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.6686847686136801</v>
+        <v>0.6817276649080455</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.011644166010271</v>
+        <v>1.024710420310747</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.108778076249841</v>
+        <v>1.121959085545079</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.476101170625611</v>
+        <v>1.489299909580375</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.941357849498559</v>
+        <v>1.95476297715139</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.438759082267737</v>
+        <v>2.452216375977954</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.459052533598957</v>
+        <v>2.472504822319067</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.550743315145532</v>
+        <v>2.584516164865121</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.459167719094168</v>
+        <v>2.434697018232654</v>
       </c>
     </row>
     <row r="20">
@@ -2945,202 +2945,202 @@
         <v>2657</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.299962504686917</v>
+        <v>-0.3070029870560944</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.09603832939141199</v>
+        <v>0.08862528547568616</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3594064146381797</v>
+        <v>0.3518361690661322</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8105526730168577</v>
+        <v>0.8028263069049402</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.518162317944757</v>
+        <v>0.5104674875448509</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.362345882647709</v>
+        <v>1.354370020899587</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.749605007414957</v>
+        <v>1.741467300216861</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.942739257321129</v>
+        <v>1.934460190269917</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.279296822495688</v>
+        <v>2.270877959717652</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.729962766365148</v>
+        <v>2.721252959178507</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.03661464029301</v>
+        <v>3.027756276766056</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.033361365572205</v>
+        <v>3.046813654292315</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.838925347024748</v>
+        <v>2.852481393376351</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.900464518969827</v>
+        <v>2.890034883271674</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0009288</t>
+          <t>X &gt; -0.0009283</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2346</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4776992010124346</v>
+        <v>0.4677475248326388</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.5022067504775691</v>
+        <v>0.4919386234306771</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.022634228538436</v>
+        <v>1.01206492052151</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.686471090371739</v>
+        <v>1.675637106772953</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.086849236948183</v>
+        <v>1.076162804621383</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.961064844574167</v>
+        <v>1.950055159393578</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.411042476931293</v>
+        <v>2.399818479007735</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.819596150511963</v>
+        <v>2.808103917232266</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.29436377712824</v>
+        <v>3.2826506865539</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.875221927236183</v>
+        <v>3.863095167794036</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.420659937487663</v>
+        <v>4.408254827178467</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.497668840783653</v>
+        <v>4.511121129503763</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.205291467690422</v>
+        <v>4.218847514042025</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.241884070213928</v>
+        <v>4.231454434515776</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0008768</t>
+          <t>X &gt; 0.0008772</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1981</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1434275763244273</v>
+        <v>0.1295257365339211</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6186061572780304</v>
+        <v>0.6040304730869082</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.407610561838027</v>
+        <v>1.392523476571405</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.119306094446337</v>
+        <v>2.103884566356307</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.062258273235059</v>
+        <v>2.046711981535822</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.589796035218342</v>
+        <v>2.574051612529438</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.037656979316203</v>
+        <v>3.021653244955495</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.658040615555429</v>
+        <v>3.641589098646058</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.130989576834608</v>
+        <v>4.114271726392403</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.572163339013336</v>
+        <v>4.55498560619678</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>5.205696643827913</v>
+        <v>5.188132696902443</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>5.038161578053696</v>
+        <v>5.051613866773806</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.66838652288871</v>
+        <v>4.681942569240313</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.51427140892573</v>
+        <v>4.503841773227578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.002682</t>
+          <t>X &gt; 0.002683</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1664</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.5848641304774134</v>
+        <v>0.5656789515444984</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.098337349122424</v>
+        <v>1.078250536294227</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.574326421868911</v>
+        <v>1.553796348106118</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.157318600621103</v>
+        <v>2.136469528712105</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.251927311317537</v>
+        <v>2.230810585133462</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.163973551211583</v>
+        <v>2.142999323278424</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.073105808945741</v>
+        <v>3.051538702148648</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.420909472775726</v>
+        <v>3.398947450653246</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.055755492523375</v>
+        <v>4.03337243119045</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.26288948975462</v>
+        <v>4.240056456169292</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.839386165437041</v>
+        <v>4.852843459147259</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.453096245859399</v>
+        <v>4.466548534579509</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.213130096452957</v>
+        <v>4.22668614280456</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.102274505652325</v>
+        <v>4.091844869954173</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1372</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.090920839818985</v>
+        <v>1.064670076556816</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.547161979869244</v>
+        <v>1.51977332897242</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.207878606059495</v>
+        <v>2.179793158313444</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.887266542183561</v>
+        <v>2.858725094263427</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.608291147045549</v>
+        <v>2.579662952966736</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.00276530850342</v>
+        <v>1.974694644817383</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.613750407298802</v>
+        <v>2.585167612973486</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.843298515729153</v>
+        <v>2.814293472357988</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.261545404795427</v>
+        <v>3.232178591209042</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.620228579236574</v>
+        <v>3.590156738534688</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.362997120808203</v>
+        <v>4.37645441451842</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.032948791273171</v>
+        <v>4.046401079993281</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.612694180328269</v>
+        <v>3.626250226679872</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.060666241467523</v>
+        <v>3.050236605769371</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1128</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.203744778381576</v>
+        <v>1.216267068057199</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.665913176957929</v>
+        <v>1.629728862317307</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.554793081569564</v>
+        <v>2.517531777990385</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.794538423992897</v>
+        <v>3.756226414776584</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.68912442264083</v>
+        <v>2.651399240127098</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.97648428532986</v>
+        <v>1.939538585272771</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.73828781679196</v>
+        <v>2.700572790527815</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.410549615812577</v>
+        <v>2.372781002526935</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.577894652960403</v>
+        <v>2.539896387096995</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.79159925516651</v>
+        <v>2.805004382819341</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.916633164891486</v>
+        <v>3.930090458601704</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.79853405273338</v>
+        <v>2.81198634145349</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.935017030440953</v>
+        <v>1.948573076792556</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.120908575483206</v>
+        <v>1.110478939785054</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>897</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.8524173027989832</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>1.463453431957376</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.277897138006949</v>
+        <v>3.290904269424551</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.86972905554228</v>
+        <v>2.882839859917219</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.278282104369055</v>
+        <v>1.29132500066342</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.256828574959833</v>
+        <v>2.206614641397252</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.298500598312806</v>
+        <v>2.247765006385698</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.524525265640968</v>
+        <v>2.473416600305754</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.789227282396766</v>
+        <v>2.802632410049597</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.253370279149422</v>
+        <v>3.26682757285964</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.841822555781356</v>
+        <v>2.855274844501466</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.418223463231108</v>
+        <v>1.431779509582711</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.6646003139020422</v>
+        <v>0.6541706782038901</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>697</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.231490046552203</v>
+        <v>1.244012336227826</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.771778897771327</v>
+        <v>2.784688707347378</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.669173801489926</v>
+        <v>4.682180932907528</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.088825214899714</v>
+        <v>6.101804357298178</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.547538670314651</v>
+        <v>4.56064947468959</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.12578290029392</v>
+        <v>3.138825796588286</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.757381561245147</v>
+        <v>3.770447815545623</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.374061465280043</v>
+        <v>3.303379171758884</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.45653360205327</v>
+        <v>3.469732341008033</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.46724055475849</v>
+        <v>3.480645682411321</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.410263414085101</v>
+        <v>4.423720707795319</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.727286456652912</v>
+        <v>3.740738745373022</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.733143753885912</v>
+        <v>2.746699800237515</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.404672833651446</v>
+        <v>1.394243197953294</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>531</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.555525898245769</v>
+        <v>1.568048187921391</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.768811042343664</v>
+        <v>2.781720851919715</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.445505424259316</v>
+        <v>4.458512555676919</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.329054225416719</v>
+        <v>5.342033367815183</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.849013424657166</v>
+        <v>3.862124229032105</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.769807528097871</v>
+        <v>3.782850424392237</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.003341230787932</v>
+        <v>5.016407485088408</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.536157832006431</v>
+        <v>4.549338841301669</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.47515794582413</v>
+        <v>4.488356684778893</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.319948015033482</v>
+        <v>5.333353142686313</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.245138193540761</v>
+        <v>6.258595487250979</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.71454959947377</v>
+        <v>5.72800188819388</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.352675402841484</v>
+        <v>4.366231449193087</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.095805398017959</v>
+        <v>3.085375762319806</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>399</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.140646892822602</v>
+        <v>1.153169182498225</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.787218643266876</v>
+        <v>2.800128452842927</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.896109335166521</v>
+        <v>3.909116466584123</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.276989034190059</v>
+        <v>4.289968176588523</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.485434987037692</v>
+        <v>2.498545791412631</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.204408871641476</v>
+        <v>5.217475125941952</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.737225472859976</v>
+        <v>4.750406482155213</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.430611551589948</v>
+        <v>6.443810290544711</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.334872331474308</v>
+        <v>7.348277459127139</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.88450497206901</v>
+        <v>8.897962265779228</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.41763499658235</v>
+        <v>8.431087285302461</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.491114721477054</v>
+        <v>5.504670767828657</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.738329788089182</v>
+        <v>4.72790015239103</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>305</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.018028484144395</v>
+        <v>-1.005506194468772</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.006651277436525049</v>
+        <v>0.006258532139526096</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.237824278261961</v>
+        <v>1.250831409679563</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.351683968246519</v>
+        <v>2.364663110644983</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4818192140387723</v>
+        <v>-0.468708409663833</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.454966985971971</v>
+        <v>1.468009882266337</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.993184088371827</v>
+        <v>4.006250342672303</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.727295885375241</v>
+        <v>7.740494624330005</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.18864611018337</v>
+        <v>8.202051237836201</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>10.60684360553793</v>
+        <v>10.62030089924815</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.985489057965324</v>
+        <v>9.998941346685434</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.630808217512225</v>
+        <v>5.644364263863828</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.569054139952442</v>
+        <v>4.55862450425429</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>220</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.766165592937249</v>
+        <v>-4.753643303261626</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.9231937513560453</v>
+        <v>-0.9102839417799942</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.863517003407182</v>
+        <v>-0.8505098719895798</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1758270382912173</v>
+        <v>0.1888061806896815</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.726230540417305</v>
+        <v>-1.713119736042366</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.298484124571075</v>
+        <v>1.311527020865441</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.395568589116984</v>
+        <v>4.40863484341746</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.412839849607721</v>
+        <v>8.426038588562484</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.92635102821616</v>
+        <v>8.939756155868992</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>11.4488704311713</v>
+        <v>11.46232772488152</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.11961722488039</v>
+        <v>10.1330695136005</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.699362613935477</v>
+        <v>4.71291866028708</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.039993037120851</v>
+        <v>4.029563401422699</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>168</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-3.904642544532727</v>
+        <v>-3.891635413115125</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.774389411925227</v>
+        <v>-3.761410269526763</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.503286817473587</v>
+        <v>-5.490176013098647</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-4.015368689281736</v>
+        <v>-4.002325792987371</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.6618023553507513</v>
+        <v>0.6748686096512273</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.575571337521623</v>
+        <v>2.588752346816861</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.681238118005993</v>
+        <v>6.694436856960756</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.42635102821616</v>
+        <v>6.439756155868992</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.98350246580335</v>
+        <v>10.99695975951357</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.041695146958304</v>
+        <v>8.055147435678414</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.264297678870541</v>
+        <v>2.277853725222144</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.109257106384923</v>
+        <v>3.098827470686771</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>124</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-5.719244771822879</v>
+        <v>-5.706722482147256</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-6.524366771883905</v>
+        <v>-6.511456962307854</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-10.95149354299663</v>
+        <v>-10.93848641157903</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.788982345872995</v>
+        <v>-6.776003203474531</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-6.52095194804194</v>
+        <v>-6.507841143667001</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-7.029961623229504</v>
+        <v>-7.016918726935138</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.469534050179213</v>
+        <v>-1.456467795878737</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.289089002652204</v>
+        <v>1.302270011947442</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.066798793889248</v>
+        <v>6.079997532844011</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.216673608861321</v>
+        <v>5.230078736514152</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.46353318776954</v>
+        <v>11.47699048147976</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9.885013119308525</v>
+        <v>9.898465408028635</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.206693992234598</v>
+        <v>2.220250038586201</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.069318550317334</v>
+        <v>4.058888914619182</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>103</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-3.949748999821622</v>
+        <v>-3.937226710146</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.561322612785879</v>
+        <v>-5.548412803209828</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-10.81056025142131</v>
+        <v>-10.79755312000371</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-8.738559545998271</v>
+        <v>-8.725580403599807</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-9.27698076107044</v>
+        <v>-9.263869956695501</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.008665036947015</v>
+        <v>-7.99562214065265</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.297282249364926</v>
+        <v>-1.28421599506445</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.11902949748464</v>
+        <v>2.132210506779877</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.941524756933404</v>
+        <v>5.954723495888167</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.120525785497712</v>
+        <v>4.133930913150543</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.71188896603451</v>
+        <v>10.72534625974473</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.804524550564409</v>
+        <v>8.817976839284519</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.55902722117289</v>
+        <v>2.572583267524493</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.750496126264714</v>
+        <v>4.740066490566562</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-1.302962129733785</v>
+        <v>-1.290439840058163</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-5.295488123650422</v>
+        <v>-5.282578314074371</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-10.45226159215178</v>
+        <v>-10.43925446073418</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-11.51248465002047</v>
+        <v>-11.499505507622</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-10.86042967461645</v>
+        <v>-10.84731887024151</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-10.56298773690079</v>
+        <v>-10.54994484060642</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.123911930363541</v>
+        <v>-1.110845676063065</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>6.681238118005993</v>
+        <v>6.694436856960756</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>3.450160552025686</v>
+        <v>3.463565679678517</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13.95969294199381</v>
+        <v>13.97315023570403</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>9.232171337434494</v>
+        <v>9.245623626154604</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>4.050011964584819</v>
+        <v>4.063568010936422</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>6.680685677813493</v>
+        <v>6.670256042115341</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MACD Histogram-12-26 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MACD Histogram-12-26 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11.79227596550432</v>
+        <v>11.80479825517994</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.97630983641966</v>
+        <v>10.98931696783726</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18.2494201118843</v>
+        <v>18.26239925428276</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>16.52052270633594</v>
+        <v>16.53363351071088</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>13.24653607262303</v>
+        <v>13.2595789689174</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.78084997439837</v>
+        <v>10.79391622869885</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10.25266668943457</v>
+        <v>10.26586542838933</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>6.816835799136676</v>
+        <v>6.830293092846894</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.041695146958304</v>
+        <v>8.055147435678414</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1.669059583632446</v>
+        <v>1.682615629984049</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>106</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.940523943940967</v>
+        <v>6.95304623361659</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.385554104561614</v>
+        <v>4.398463914137665</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.651062756455588</v>
+        <v>9.66406988787319</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15.44169324755365</v>
+        <v>15.45467238995212</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.90327203248148</v>
+        <v>14.91638283685642</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>12.37052529095186</v>
+        <v>12.38356818724623</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.4556028944343</v>
+        <v>9.468669148734776</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.931815722067903</v>
+        <v>9.94499673136314</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.984023383055408</v>
+        <v>7.997222122010172</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.020690650857674</v>
+        <v>9.034095778510505</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.042352420879709</v>
+        <v>5.055809714589927</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.020131804640236</v>
+        <v>6.033584093360346</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.826292288034956</v>
+        <v>1.839848334386559</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1892211674810582</v>
+        <v>0.1787915317829061</v>
       </c>
     </row>
     <row r="8">
@@ -4015,98 +4015,98 @@
         <v>125</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.306561679790022</v>
+        <v>8.319083969465645</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.494988066825769</v>
+        <v>7.50789787640182</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.10011936022919</v>
+        <v>11.11312649164679</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15.23037249283667</v>
+        <v>15.24335163523514</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.09195127776451</v>
+        <v>13.10506208213945</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>10.18939321548017</v>
+        <v>10.20243611177453</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8.504659498207893</v>
+        <v>8.517725752508369</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>8.837476099426389</v>
+        <v>8.850657108721627</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.176476213244086</v>
+        <v>7.18967495219885</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.92635102821616</v>
+        <v>7.939756155868992</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.321597703898583</v>
+        <v>5.3350549976088</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.755980861244012</v>
+        <v>7.769433149964122</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.935726250299112</v>
+        <v>4.949282296650715</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.0226</t>
+          <t>X &lt; -0.02259</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>143</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.548519721748065</v>
+        <v>5.561042011423687</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.132750304588008</v>
+        <v>8.145660114164059</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.835783695893511</v>
+        <v>9.848790827311113</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>14.16184102430521</v>
+        <v>14.17482016670368</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>12.92411910993235</v>
+        <v>12.93722991430729</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>11.1236589497459</v>
+        <v>11.13670184604027</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.941023134571523</v>
+        <v>8.954089388871999</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8.473839735790023</v>
+        <v>8.48702074508526</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6.314937751705628</v>
+        <v>6.328136490660391</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.562714664579794</v>
+        <v>7.576119792232625</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.260059242360121</v>
+        <v>5.273516536070339</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.490246595509745</v>
+        <v>9.503698884229856</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>7.671390585963444</v>
+        <v>7.684946632315047</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.522510519638338</v>
+        <v>6.512080883940186</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>168</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.609273781111476</v>
+        <v>6.622183590687527</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.404881264991083</v>
+        <v>7.417888396408685</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.916086778550969</v>
+        <v>9.929065920949434</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.3776655634788</v>
+        <v>9.390776367853739</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.103678929765877</v>
+        <v>6.116721826060243</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.828469022017416</v>
+        <v>4.841535276317892</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.361285623235915</v>
+        <v>4.374466632531153</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.300285737053613</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.831112932978066</v>
+        <v>5.844518060630897</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.245407227708107</v>
+        <v>3.258864521418325</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.255980861244012</v>
+        <v>6.269433149964122</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.240488155061016</v>
+        <v>5.254044201412619</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.704495201623011</v>
+        <v>3.694065565924859</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>215</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.785631447231886</v>
+        <v>3.798153736907508</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.034522950546702</v>
+        <v>4.047432760122753</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.895468197438483</v>
+        <v>6.908475328856085</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.28153528353435</v>
+        <v>10.29451442593281</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.812881510322647</v>
+        <v>8.825992314697586</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>5.402436111774534</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.444194381928824</v>
+        <v>3.4572606362293</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.907243541286853</v>
+        <v>3.920424550582091</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.846243655104551</v>
+        <v>3.859442394059315</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.461234749146392</v>
+        <v>3.474639876799223</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.396016308549747</v>
+        <v>1.409473602259965</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.290864582174244</v>
+        <v>3.304316870894354</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.7947499081567884</v>
+        <v>0.7843202724586362</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>272</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.550679326848844</v>
+        <v>1.563201616524466</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.512635125649297</v>
+        <v>2.525544935225348</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.117766419052707</v>
+        <v>2.130773550470309</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.39507837518962</v>
+        <v>7.408057517588084</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.224304218940979</v>
+        <v>7.237415023315918</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.580569686068408</v>
+        <v>4.593612582362773</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.495835968796129</v>
+        <v>4.508902223096605</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.6610055111911</v>
+        <v>3.674186520486337</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.600005625008798</v>
+        <v>3.613204363963561</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.749880439980871</v>
+        <v>2.763285567633702</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.809832998016233</v>
+        <v>1.823290291726451</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.211863214185193</v>
+        <v>2.225315502905303</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.159255662063821</v>
+        <v>2.172811708415423</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.306035817869514</v>
+        <v>1.295606182171362</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>357</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.72785019519619</v>
+        <v>0.7403724848718127</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.917397030411202</v>
+        <v>1.930306839987253</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.36286445826839</v>
+        <v>2.375871589685993</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.134574173508945</v>
+        <v>6.147553315907409</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.716601137708487</v>
+        <v>6.729711942083426</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.773146716880731</v>
+        <v>4.786189613175097</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.567964820336748</v>
+        <v>3.581031074637224</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.540557331919381</v>
+        <v>2.553738341214618</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3215630024421827</v>
+        <v>-0.3083642634874195</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.891576142652184</v>
+        <v>-0.8781710149993529</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.376441511787689</v>
+        <v>-1.362984218077472</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.061946309624332</v>
+        <v>-1.048494020904222</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.3617527412975292</v>
+        <v>-0.3481966949459263</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.9523675434750203</v>
+        <v>-0.9627971791731724</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>432</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2843394575678033</v>
+        <v>0.2968617472434261</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.144988066825768</v>
+        <v>2.157897876401819</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.907526767636583</v>
+        <v>2.920533899054185</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.047039159503342</v>
+        <v>6.060018301901806</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5.740099425912661</v>
+        <v>5.7532102302876</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.417170993257947</v>
+        <v>4.430213889552313</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.017622461170852</v>
+        <v>2.030688715471328</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.087476099426389</v>
+        <v>1.100657108721627</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1309311941633169</v>
+        <v>-0.1177324552085537</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.675500823635687</v>
+        <v>-1.662095695982856</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.343217110916235</v>
+        <v>-2.329759817206018</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.308833953570804</v>
+        <v>-2.295381664850694</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.571681157108294</v>
+        <v>-1.558125110756691</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.553441306313488</v>
+        <v>-1.56387094201164</v>
       </c>
     </row>
     <row r="15">
@@ -4376,257 +4376,257 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>1.961428014834269</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.902563824401525</v>
+        <v>2.807708840484992</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.833452693562514</v>
+        <v>3.925224790323533</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.100069462533646</v>
+        <v>5.189665434857069</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.940436126249359</v>
+        <v>5.029447715409766</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.775756851843802</v>
+        <v>2.869354826330301</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9864776800260699</v>
+        <v>1.083321215646365</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.04888753693724368</v>
+        <v>0.04914482138703846</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.867463180695303</v>
+        <v>-0.7679810024325278</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.853952002086871</v>
+        <v>-2.752115299707569</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.62688714458627</v>
+        <v>-3.523924208440349</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.971291866028714</v>
+        <v>-3.867617889733417</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.012758598185741</v>
+        <v>-3.909696909398434</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.66312926751948</v>
+        <v>-3.494925342347713</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.009957</t>
+          <t>X &lt; -0.009956</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.095078426201511</v>
+        <v>1.107600715877133</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.397380411323375</v>
+        <v>1.410290220899427</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.597408036465225</v>
+        <v>2.610415167882827</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.206130068594256</v>
+        <v>3.21910921099272</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.262605185260526</v>
+        <v>4.275715989635465</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.64617152489005</v>
+        <v>2.659214421184416</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.126031109053187</v>
+        <v>1.139097363353663</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.02088917757631492</v>
+        <v>0.03407018687155272</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.5185796081275242</v>
+        <v>-0.505380869172761</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.166152959024672</v>
+        <v>-2.15274783137184</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.327844082385312</v>
+        <v>-3.314386788675094</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.931419457735252</v>
+        <v>-3.917967169015142</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.873205169158624</v>
+        <v>-3.859649122807021</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.219664238510866</v>
+        <v>-3.155444573058951</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.008151</t>
+          <t>X &lt; -0.00815</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2843394575678033</v>
+        <v>0.2968617472434261</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.061654733492432</v>
+        <v>0.07456454306848315</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8031496632594752</v>
+        <v>0.8161567946770774</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.312190674654858</v>
+        <v>1.325169817053322</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.910133095946328</v>
+        <v>1.923243900321268</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.6924235185104664</v>
+        <v>0.7054664148048317</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.7811990876506982</v>
+        <v>-0.7681328333502222</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.500907738957444</v>
+        <v>-1.487726729662207</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.814432877665006</v>
+        <v>-1.801234138710242</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.422133820268691</v>
+        <v>-3.40872869261586</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.131937649636768</v>
+        <v>-4.11848035592655</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.728867623604472</v>
+        <v>-4.715415334884362</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.149122234549374</v>
+        <v>-5.135566188197771</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.834274288473907</v>
+        <v>-4.783567911708609</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.006346</t>
+          <t>X &lt; -0.006345</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1888291017731021</v>
+        <v>-0.2286637782821046</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.105408908509141</v>
+        <v>1.063053031556976</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.011141404317357</v>
+        <v>0.968581947102237</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.9409937353216478</v>
+        <v>0.8986068904903917</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.805378131471926</v>
+        <v>1.761718738796105</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.001388347646077648</v>
+        <v>-0.0430093336709092</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.589128076942416</v>
+        <v>-1.629221194438578</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.056311475723916</v>
+        <v>-2.096289838225317</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.019114969120636</v>
+        <v>-3.058172895648994</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.570642959759795</v>
+        <v>-4.608792392679561</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.576999490490202</v>
+        <v>-5.514194251640447</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.280616900085924</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-6.614123298346833</v>
+        <v>-6.700767753399333</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.00454</t>
+          <t>X &lt; -0.004539</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2265616797900236</v>
+        <v>0.1969416832945825</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3749880668257646</v>
+        <v>0.4242847668894285</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2201193602291767</v>
+        <v>0.1893854844525364</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.2096275071633258</v>
+        <v>-0.2399417300726086</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.05195127776450903</v>
+        <v>0.02112922842242426</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.570606784519832</v>
+        <v>-1.599961969760237</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.37534050179211</v>
+        <v>-2.404096789458066</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.602523900573615</v>
+        <v>-2.631357279767585</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.463523786755914</v>
+        <v>-3.491699947881081</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.553648971783844</v>
+        <v>-4.581426897688168</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.718402296101416</v>
+        <v>-5.745360669857227</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.764019138755984</v>
+        <v>-5.79091856866097</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.983729314152455</v>
+        <v>-6.051197319656247</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.773526776398967</v>
+        <v>-5.704982053122755</v>
       </c>
     </row>
     <row r="20">
@@ -4636,205 +4636,205 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5249343832021012</v>
+        <v>0.5374566728777239</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.168004059158477</v>
+        <v>-0.1550942495824259</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6284895636553429</v>
+        <v>-0.6154824322377408</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.416871601651515</v>
+        <v>-1.403892459253051</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.9054240503194819</v>
+        <v>-0.8923132459445426</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.379635655910903</v>
+        <v>-2.366592759616537</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.054920554285545</v>
+        <v>-3.041854299985069</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.390870357266529</v>
+        <v>-3.377689347971291</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.976804626650917</v>
+        <v>-3.963605887696154</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.76131301377859</v>
+        <v>-4.747907886125759</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.294150327597485</v>
+        <v>-5.280693033887268</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.291950852478905</v>
+        <v>-5.311931679432199</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.955995168886176</v>
+        <v>-4.976390717137861</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.066754915780947</v>
+        <v>-5.04521858400318</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0009288</t>
+          <t>X &lt; -0.0009283</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.6133293283843599</v>
+        <v>-0.6008070387087372</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6445214699589741</v>
+        <v>-0.6316116603829229</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.311869740588264</v>
+        <v>-1.298862609170662</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.16254303849847</v>
+        <v>-2.149563896100005</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.393062346213689</v>
+        <v>-1.37995154183875</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.51251414146806</v>
+        <v>-2.499471245173694</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.087711073999195</v>
+        <v>-3.074644819698719</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.60939038558724</v>
+        <v>-3.596209376292002</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.215349399834935</v>
+        <v>-4.202150660880172</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.956482759249781</v>
+        <v>-4.94307763159695</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.651699298826209</v>
+        <v>-5.638242005115991</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.753288495353587</v>
+        <v>-5.767351591180294</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.382222467649612</v>
+        <v>-5.396628281320936</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.432019666332899</v>
+        <v>-5.415707639593016</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0008768</t>
+          <t>X &lt; 0.0008772</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.1298019565736084</v>
+        <v>-0.1172796668979856</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5595573877196927</v>
+        <v>-0.5466475781436415</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.272607912498103</v>
+        <v>-1.259600781080501</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.915082052617869</v>
+        <v>-1.902102910219405</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.862594176780952</v>
+        <v>-1.849483372406013</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.337879511792558</v>
+        <v>-2.324836615498192</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.740795047246657</v>
+        <v>-2.727728792946181</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.298887536937244</v>
+        <v>-3.285706527642006</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.723523786755912</v>
+        <v>-3.710325047801149</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.119103517238386</v>
+        <v>-4.105698389585555</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.687493205192332</v>
+        <v>-4.674035911482115</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.538698538483132</v>
+        <v>-4.548748668217691</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.207494859800974</v>
+        <v>-4.217793646960025</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.070446818881138</v>
+        <v>-4.059194973959883</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.002682</t>
+          <t>X &lt; 0.002683</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3885932050392</v>
+        <v>-0.3760709153635773</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.7293169371456472</v>
+        <v>-0.716407127569596</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.044757526188619</v>
+        <v>-1.031750394771016</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.430787157679603</v>
+        <v>-1.417808015281139</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.492639667430097</v>
+        <v>-1.479528863055158</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.433482082375271</v>
+        <v>-1.420439186080905</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.034498563746041</v>
+        <v>-2.021432309445565</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.263397609866701</v>
+        <v>-2.250216600571463</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.681824025040271</v>
+        <v>-2.668625286085508</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.817096152085661</v>
+        <v>-2.80369102443283</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.199339920257167</v>
+        <v>-3.206962476577061</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.94513201633945</v>
+        <v>-2.952855288653275</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.787534187076638</v>
+        <v>-2.79539178919984</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.715268407878057</v>
+        <v>-2.707288216144626</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2806</v>
+        <v>2807</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5361429465444942</v>
+        <v>-0.5236206568688715</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7598162036368663</v>
+        <v>-0.7469063940608152</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.083510533009253</v>
+        <v>-1.070503401591651</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.415890852359048</v>
+        <v>-1.402911709960584</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.278155483801328</v>
+        <v>-1.265044679426389</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.9807135460856671</v>
+        <v>-0.9676706497913017</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.278970395030541</v>
+        <v>-1.265904140730065</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.390281907691048</v>
+        <v>-1.37710089839581</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.593630548321748</v>
+        <v>-1.580431809366985</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.767599149719778</v>
+        <v>-1.754194022066947</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.131018885635065</v>
+        <v>-2.136831123387644</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.970514865251715</v>
+        <v>-1.976383866767819</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.765805634275168</v>
+        <v>-1.771800324431908</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.496519630539353</v>
+        <v>-1.490888715039389</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4476118062983545</v>
+        <v>-0.4521202190160309</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6189235534688322</v>
+        <v>-0.6060137438927811</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9483258116202506</v>
+        <v>-0.9353186802026485</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.407270715019294</v>
+        <v>-1.39429157262083</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9964284276364737</v>
+        <v>-0.9833176232615344</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7317197141433951</v>
+        <v>-0.7186768178490297</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.012852776751195</v>
+        <v>-0.9997865224507194</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.8908381395261458</v>
+        <v>-0.877657130230908</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.9518380257084473</v>
+        <v>-0.9386392867536841</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.031081846701973</v>
+        <v>-1.035693925964068</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.447088833933059</v>
+        <v>-1.451585473903975</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.03432058043358</v>
+        <v>-1.038952044926155</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7154045264953766</v>
+        <v>-0.7201803507935907</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.4145524174245949</v>
+        <v>-0.4105605519755926</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2296887000337406</v>
+        <v>-0.2330423974845388</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.396805246244142</v>
+        <v>-0.4002151591496812</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8969618194606994</v>
+        <v>-0.9002473685355952</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.084955974316607</v>
+        <v>-1.088177704989853</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.785748752658364</v>
+        <v>-0.789098501802151</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3501076974839208</v>
+        <v>-0.353572406631308</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6174342327720268</v>
+        <v>-0.6043679784715508</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6281355865139631</v>
+        <v>-0.6149545772187253</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6891354726962646</v>
+        <v>-0.6759367337415014</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7616246186635891</v>
+        <v>-0.7650521216720918</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.8886337211927682</v>
+        <v>-0.8920378486621345</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.776458980364275</v>
+        <v>-0.7798969352977494</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.3876131768794409</v>
+        <v>-0.3911989704830106</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1816965807894277</v>
+        <v>-0.1787907063829621</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2460864736597372</v>
+        <v>-0.2485176332819208</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5540382791077931</v>
+        <v>-0.5564594095987516</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.9335672625150195</v>
+        <v>-0.9358998542867809</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.217765042979934</v>
+        <v>-1.220011298021802</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.9097684126912142</v>
+        <v>-0.9121298949379195</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6255150414005684</v>
+        <v>-0.6279450862764833</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.752122836176973</v>
+        <v>-0.7545219539136525</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6744252484371032</v>
+        <v>-0.6612442391418654</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.6911084109670469</v>
+        <v>-0.6935484490056254</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.6934481109516994</v>
+        <v>-0.6959294436720285</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.8823058552288643</v>
+        <v>-0.8847441415590609</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.7458853460485528</v>
+        <v>-0.7483624872344947</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.5470997117916454</v>
+        <v>-0.5496554007365972</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2812573872608581</v>
+        <v>-0.2790888882749627</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3647</v>
+        <v>3648</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.225678757368442</v>
+        <v>-0.2274333755220539</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4018143382029251</v>
+        <v>-0.4035775334342446</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6453153035215067</v>
+        <v>-0.6470265556339001</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7737839195231757</v>
+        <v>-0.7754564566183291</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5590334049488419</v>
+        <v>-0.5607842399825174</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5476792879398076</v>
+        <v>-0.5494238444617849</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7270865335381416</v>
+        <v>-0.7287858753986072</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6593758031194668</v>
+        <v>-0.661110816839404</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6506869850034462</v>
+        <v>-0.6524274294053143</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7737311410525365</v>
+        <v>-0.7754683786326524</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.908539282402792</v>
+        <v>-0.9102476591975517</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.831577373888905</v>
+        <v>-0.8333065760632721</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6335719953149166</v>
+        <v>-0.6353710330286546</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.4507465495880183</v>
+        <v>-0.4491048601402952</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3779</v>
+        <v>3780</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.120020598690985</v>
+        <v>-0.1213062229941428</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2933527403491212</v>
+        <v>-0.2946337691678025</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4101708772378458</v>
+        <v>-0.4114316724260263</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4503876021751978</v>
+        <v>-0.4516351721527201</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.261797402277729</v>
+        <v>-0.2631089392382222</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3460173997825677</v>
+        <v>-0.3472998966731922</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5484836607989791</v>
+        <v>-0.5497154938607878</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4993799111416379</v>
+        <v>-0.5006371332223765</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>-0.6792814546703667</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.7736225377367845</v>
+        <v>-0.7748315819745528</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.9373129253980821</v>
+        <v>-0.9384845212915423</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.8882931403428671</v>
+        <v>-0.8894774793325411</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.5796176650448075</v>
+        <v>-0.5808949051477583</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5002893848763108</v>
+        <v>-0.4990561271968303</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3873</v>
+        <v>3874</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.07990187536388049</v>
+        <v>0.07889873663827984</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.0005221723598722861</v>
+        <v>-0.000491212635751026</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.0972029878655718</v>
+        <v>-0.09819911967883144</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1847189313199067</v>
+        <v>-0.1856905892756799</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.03785545087114883</v>
+        <v>0.03681588074876174</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1143429349965146</v>
+        <v>-0.1153382313475646</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3138972028230427</v>
+        <v>-0.3148431730262899</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3803635499677895</v>
+        <v>-0.3813016541649645</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6077424561731348</v>
+        <v>-0.6086235783502545</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6441932070172598</v>
+        <v>-0.6450813892573635</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.8346458461530162</v>
+        <v>-0.8354892376246212</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7859546226269529</v>
+        <v>-0.7868104000874752</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.4433135018950054</v>
+        <v>-0.4442660904460567</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3598144881707981</v>
+        <v>-0.3589004836854812</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3958</v>
+        <v>3959</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.2640534954535809</v>
+        <v>0.2632934357294943</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.05115935146052664</v>
+        <v>0.05043124331191251</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.04786438416467576</v>
+        <v>0.04713152943015331</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.00974847490525832</v>
+        <v>-0.01046544715337205</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09573247262208184</v>
+        <v>0.09498143697815919</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.07202887226566901</v>
+        <v>-0.07273404199406031</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2438903126370064</v>
+        <v>-0.2445536221764542</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.268477482813779</v>
+        <v>-0.269141125830707</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4670261839297751</v>
+        <v>-0.4676408903843949</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4956580581038779</v>
+        <v>-0.4962771522309311</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6358877795651949</v>
+        <v>-0.6364745329313308</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5622009569378079</v>
+        <v>-0.5628061835375249</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2611416456342042</v>
+        <v>-0.2618288144604008</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.2245574704816988</v>
+        <v>-0.2239211791646767</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2532681177716327</v>
+        <v>0.2526823790083981</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.072014421873007</v>
+        <v>0.07145740908886467</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.163138509694484</v>
+        <v>0.1625546368481778</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1577356769162819</v>
+        <v>0.1571541719175613</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2300453310115884</v>
+        <v>0.2294401915921824</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1678899800396465</v>
+        <v>0.1673029940835633</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.02767806713937659</v>
+        <v>-0.02821750284255131</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1077430240795891</v>
+        <v>-0.1082674618534298</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2795636373163148</v>
+        <v>-0.2800461633390015</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2689653644096452</v>
+        <v>-0.2694592862231602</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4598127122489331</v>
+        <v>-0.4602613950170067</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3367409732524962</v>
+        <v>-0.3372202265621738</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.09483969335584419</v>
+        <v>-0.09538370534330198</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.130263140616627</v>
+        <v>-0.1297938207617477</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1743757933872701</v>
+        <v>0.1739512261028224</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1989723265404777</v>
+        <v>0.1985297918185864</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.3340676997125769</v>
+        <v>0.3335888625272574</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2071441463799886</v>
+        <v>0.2066972686914781</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1990150237649999</v>
+        <v>0.1985660191473144</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2146024720040458</v>
+        <v>0.214151592946088</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.04487126870777303</v>
+        <v>0.0444613507358369</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.03937119121400912</v>
+        <v>-0.03976396983045305</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1853370412520974</v>
+        <v>-0.1856945059292272</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1594055020943301</v>
+        <v>-0.1597757485409588</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.3503766613959698</v>
+        <v>-0.3507015327016916</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.302204543095236</v>
+        <v>-0.3025412153304288</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.0674796683198835</v>
+        <v>-0.06787746666289252</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1244685496397011</v>
+        <v>-0.1241189211868701</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4075</v>
+        <v>4076</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.09951667000529341</v>
+        <v>0.09917690172292026</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1401556714257239</v>
+        <v>0.1397961151493732</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2725128991425407</v>
+        <v>0.2721184172646005</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2203357731304436</v>
+        <v>0.2199546699879562</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2339689075392357</v>
+        <v>0.2335810539876775</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2020309818284431</v>
+        <v>0.2016525662309476</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.03273397150529433</v>
+        <v>0.03239633786227358</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.05348199907888329</v>
+        <v>-0.05380149000448853</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1499943749912021</v>
+        <v>-0.1502907424838185</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1040485795308328</v>
+        <v>-0.1043614911898345</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2705553122858149</v>
+        <v>-0.2708287974390089</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2224346403503006</v>
+        <v>-0.2227198662202738</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.06466629140844304</v>
+        <v>-0.06499290570395289</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1200738898172418</v>
+        <v>-0.1197808754976322</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.02664933501281297</v>
+        <v>0.02638679322416237</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1083343892807136</v>
+        <v>0.1080439684398016</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.213883063030643</v>
+        <v>0.213564874501138</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.2356356507314104</v>
+        <v>0.2353126583776515</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2223436735724533</v>
+        <v>0.2220211464669362</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2163069161140072</v>
+        <v>0.2159871719743833</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.02302087348221704</v>
+        <v>0.02274769302518109</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.04057268106141265</v>
+        <v>-0.04083277179531564</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1369172973682566</v>
+        <v>-0.1371543160938273</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.0707207140971633</v>
+        <v>-0.07097816957624303</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2862128892183335</v>
+        <v>-0.2864188920934936</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1893316387559878</v>
+        <v>-0.1895612361720751</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.08307716850431035</v>
+        <v>-0.08333489084928658</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1370731795154683</v>
+        <v>-0.136825764966467</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/macd/macd_histogram_12_26.xlsx
+++ b/workspaces/btc_daily_14days/macd/macd_histogram_12_26.xlsx
@@ -568,1093 +568,1093 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02711</t>
+          <t>X ≈ -0.02708</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-11.5357762369031</v>
+        <v>-9.623061293305724</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.516041219237962</v>
+        <v>12.53639789416318</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.591029365812069</v>
+        <v>2.648064012243999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.72175041150853</v>
+        <v>2.777972251974937</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.721406487538218</v>
+        <v>7.042080804145485</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.020548808105197</v>
+        <v>7.31627079141554</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.400691780993348</v>
+        <v>2.503904341357135</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.935421350390172</v>
+        <v>2.039402366612045</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.6643131881549138</v>
+        <v>-2.753017135118959</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.027478569730135</v>
+        <v>5.93784865051051</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.71832793158368</v>
+        <v>0.9770084396350782</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.684366312348629</v>
+        <v>1.035404629661208</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.439583950606604</v>
+        <v>5.401405367920546</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>0.8898738493032141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02531</t>
+          <t>X ≈ -0.02527</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15.88860803337941</v>
+        <v>17.43354838126718</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>24.78157401930977</v>
+        <v>25.83010508069615</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>19.14470975061968</v>
+        <v>20.45692540019645</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>14.0288097104691</v>
+        <v>15.60347817932805</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.992296024235074</v>
+        <v>0.1524121976756092</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.962746469524056</v>
+        <v>-4.565252452924099</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.206501196848521</v>
+        <v>0.3646845604414324</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.740954789925219</v>
+        <v>-0.1003296151814013</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.680848989846211</v>
+        <v>4.856699394515665</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.832453199987036</v>
+        <v>4.034899027330859</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.887755430366077</v>
+        <v>8.828347335679183</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>17.44495995295713</v>
+        <v>18.88375797392839</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>22.29114035491844</v>
+        <v>23.49217859187979</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>22.52238636792988</v>
+        <v>23.74701670644391</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.0235</t>
+          <t>X ≈ -0.02347</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-13.54920856887126</v>
+        <v>-17.161720203645</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12.53660393655308</v>
+        <v>10.58050455347166</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.064848453145494</v>
+        <v>-1.542614419539305</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.736609766030867</v>
+        <v>4.454197062188044</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>11.7446399462714</v>
+        <v>15.70604730382707</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>17.58917145351083</v>
+        <v>21.8531889002726</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.9631888545803</v>
+        <v>15.9259942000687</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.952513993480316</v>
+        <v>9.591182157273543</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3445293916583836</v>
+        <v>-2.193470751635026</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.045624258696613</v>
+        <v>2.859551696947037</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.842444486395898</v>
+        <v>2.65639147113405</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.53642011371618</v>
+        <v>20.35353417341383</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>26.67596832185568</v>
+        <v>25.84448555602103</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>26.90835128020804</v>
+        <v>26.09995788291449</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.02169</t>
+          <t>X ≈ -0.02167</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>25</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4799968727224027</v>
+        <v>-0.5090960820919221</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.086720027174181</v>
+        <v>-2.087915515160276</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.470083963033595</v>
+        <v>-6.470280140430802</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-14.32219012076917</v>
+        <v>-14.32277398265225</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-10.87157020758543</v>
+        <v>-10.82319749513933</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-22.55336630941468</v>
+        <v>-22.52957665364688</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-18.65027848073184</v>
+        <v>-18.60243902182471</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-19.12118891874366</v>
+        <v>-19.07209297379517</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.201626853693512</v>
+        <v>-7.128486916186255</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.056465932091633</v>
+        <v>-3.957230395541181</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.258907455913018</v>
+        <v>-8.159092636949453</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-12.22463911171702</v>
+        <v>-12.10102189102597</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-8.648629343706702</v>
+        <v>-8.499983587725872</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-12.42498205312275</v>
+        <v>-12.25298329355973</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01988</t>
+          <t>X ≈ -0.01987</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.707614394350756</v>
+        <v>1.650524555616528</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.141205380708847</v>
+        <v>-4.081796032518149</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.072658260016901</v>
+        <v>5.912418942795924</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>11.57056280890094</v>
+        <v>10.19948394769554</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.790880463869243</v>
+        <v>7.635424949933032</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.842990982084999</v>
+        <v>3.751659118312475</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.488513805584923</v>
+        <v>-0.4671322013677042</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.293716880296842</v>
+        <v>3.228085628867206</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.233438705930745</v>
+        <v>3.19201901024099</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.991623874063592</v>
+        <v>-3.873913579636159</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.197285076296012</v>
+        <v>-4.078730403428352</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.290850528622229</v>
+        <v>-6.103932623254551</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.458411388679551</v>
+        <v>-2.334830735704116</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-9.616471414823913</v>
+        <v>-8.336316626888483</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01808</t>
+          <t>X ≈ -0.01806</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.844789069394089</v>
+        <v>-7.841948826231686</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.205735230080627</v>
+        <v>-4.081491895299784</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-15.84681824773891</v>
+        <v>-16.9405438889298</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.471994302260825</v>
+        <v>-2.566261700861375</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.241452973149116</v>
+        <v>0.5084564439181563</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.539036869068788</v>
+        <v>0.781319502868314</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.460127480312977</v>
+        <v>7.851351422798757</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.740858746428678</v>
+        <v>2.039293182040261</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.680713587403204</v>
+        <v>2.002947550049576</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.07983255076096185</v>
+        <v>-0.6033461973562595</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.381522637958874</v>
+        <v>2.761349186732033</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.843749815828495</v>
+        <v>-2.534248272780438</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.264219746096678</v>
+        <v>-2.929902860942811</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.224140753894787</v>
+        <v>2.675588135015339</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01628</t>
+          <t>X ≈ -0.01626</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>85</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.886632554431976</v>
+        <v>-1.915739107185509</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02491635449094787</v>
+        <v>0.0237368577683057</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.150691651156897</v>
+        <v>3.150567082692461</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.107080888165626</v>
+        <v>2.106611153024659</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.091888010823475</v>
+        <v>5.140353350747525</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.390485023205279</v>
+        <v>5.41442516524711</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6101520181996705</v>
+        <v>0.6580765566392159</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.030479067239142</v>
+        <v>-0.9813161769601635</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-12.84091384385692</v>
+        <v>-12.76780507436009</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-12.51793228573123</v>
+        <v>-12.41873213033627</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-11.55009619841977</v>
+        <v>-11.45029715078812</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-11.51873792788043</v>
+        <v>-11.39512712237777</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-8.413261881775242</v>
+        <v>-8.264619898859934</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-8.189687935476236</v>
+        <v>-8.017689175909034</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01447</t>
+          <t>X ≈ -0.01445</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.80821498473572</v>
+        <v>-2.50168390156297</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.230310315030628</v>
+        <v>2.477174171460206</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.496341358978995</v>
+        <v>4.7090658960635</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.62680631940664</v>
+        <v>4.838983613385324</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.100911479564282</v>
+        <v>0.414264718694767</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.72899043620879</v>
+        <v>2.000129908387812</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.339589442789325</v>
+        <v>-5.939614037053758</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-5.807092135979104</v>
+        <v>-6.40604080774402</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7886609472298858</v>
+        <v>0.1259514387079221</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.38773818158792</v>
+        <v>-5.954479757979371</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.925964610234224</v>
+        <v>-7.474763906412591</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-8.226123824224608</v>
+        <v>-8.733754024192137</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.315423350877822</v>
+        <v>-7.815732372580555</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.424982053121539</v>
+        <v>-4.937193819871879</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01266</t>
+          <t>X ≈ -0.01264</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.341361989374555</v>
+        <v>9.954480933170586</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.682215727335077</v>
+        <v>6.301958013966811</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8.373477505224699</v>
+        <v>9.026555617982233</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.307962192177371</v>
+        <v>1.885847243052694</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.800022980781534</v>
+        <v>2.437681724533867</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.074287135477519</v>
+        <v>-3.525321423804009</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.130327292578961</v>
+        <v>-2.546488646275591</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-4.626482062433347</v>
+        <v>-4.051980241360084</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.658902530730792</v>
+        <v>-3.049542708698212</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-7.598099134776021</v>
+        <v>-6.994708402946458</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-8.834782531776824</v>
+        <v>-8.24139472365853</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-10.86364449516757</v>
+        <v>-10.26778311897086</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-14.37868789645754</v>
+        <v>-13.78987976181032</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-12.09508514590673</v>
+        <v>-12.50298329355609</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.01086</t>
+          <t>X ≈ -0.01084</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.489589331333505</v>
+        <v>-2.995239599795319</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.113634522753969</v>
+        <v>-4.574281980506704</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.474772291738084</v>
+        <v>-4.968471586882202</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-7.399153646624654</v>
+        <v>-6.815346633244239</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.2047417306348507</v>
+        <v>-1.379408631292399</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.520525910400835</v>
+        <v>0.8690477194479058</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.437033914167941</v>
+        <v>0.8093697061788205</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.04723429901410015</v>
+        <v>-0.6435890063089857</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9109980229469059</v>
+        <v>1.296894942339144</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.081843690493365</v>
+        <v>1.463631745722992</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.18103925180786</v>
+        <v>-1.70773573018019</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.187077488482224</v>
+        <v>-4.618823113295569</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.588323504496692</v>
+        <v>-4.025497260166013</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.322941236795998</v>
+        <v>-1.797537749001634</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.009053</t>
+          <t>X ≈ -0.009038</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.774046660320316</v>
+        <v>-2.806888290360732</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.98441249810918</v>
+        <v>-5.608229951279945</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.98408234525467</v>
+        <v>-6.002757930641934</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-5.856182696725462</v>
+        <v>-6.486980442435005</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.99955116882937</v>
+        <v>-6.365161054638101</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-6.704047466039945</v>
+        <v>-6.706121057215782</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-7.999489576991699</v>
+        <v>-7.99241925739193</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-7.257708768324889</v>
+        <v>-6.622134750899377</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-6.715431514117022</v>
+        <v>-6.66090858149348</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-8.17135743140787</v>
+        <v>-8.098185332093642</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-7.16716989498245</v>
+        <v>-7.078539327795397</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-7.740739356752378</v>
+        <v>-7.022576538995636</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-9.980903112955318</v>
+        <v>-9.259840371003605</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-10.97043659857744</v>
+        <v>-10.24071335490579</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.007247</t>
+          <t>X ≈ -0.007233</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.241709424421636</v>
+        <v>-2.259667357292663</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.851862192542626</v>
+        <v>4.825641488407207</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.554744544938899</v>
+        <v>2.027123370053914</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7343171773244634</v>
+        <v>-0.250991164620153</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.147425024602065</v>
+        <v>1.669389109335306</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.914003828462896</v>
+        <v>-2.39407478016809</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.938938391331256</v>
+        <v>-4.382696590914939</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.440344801256408</v>
+        <v>-4.366639658240032</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7.897103213665986</v>
+        <v>-7.781266562503347</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-9.239402552714502</v>
+        <v>-9.57113338978246</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-10.90421787939037</v>
+        <v>-11.2260750855104</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-12.3299003670884</v>
+        <v>-12.62003441529613</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-12.75679168232723</v>
+        <v>-13.01932563797386</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-12.73566166477324</v>
+        <v>-13.2578142114306</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.005442</t>
+          <t>X ≈ -0.005429</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.876767397671451</v>
+        <v>1.420895076313911</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.10133296714698</v>
+        <v>-2.509641033580394</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.89073782814804</v>
+        <v>-3.294766014715613</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.739774461195807</v>
+        <v>-5.128081765365003</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.86183049617717</v>
+        <v>-7.188337819841905</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-7.753604558721136</v>
+        <v>-8.094879162540963</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.463686631111294</v>
+        <v>-5.800391467140649</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.743298290780515</v>
+        <v>-5.088417747543502</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.201911076112324</v>
+        <v>-5.519803001492946</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.466886001897933</v>
+        <v>-4.378183095826387</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.656043734576173</v>
+        <v>-6.15699687953316</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.847627630839852</v>
+        <v>-3.347359902401436</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.476114528746109</v>
+        <v>-2.957009229053654</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.853553481694185</v>
+        <v>-2.315975419540251</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.003636</t>
+          <t>X ≈ -0.003625</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>272</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.096831460402136</v>
+        <v>2.623890675045239</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.80982247945704</v>
+        <v>-2.245651661642924</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.304940490823441</v>
+        <v>-3.736546867510206</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-6.742139329152756</v>
+        <v>-6.171747309729895</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-5.083355809104013</v>
+        <v>-4.463690856380474</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-5.888900055200551</v>
+        <v>-5.290935807192888</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.976844836713347</v>
+        <v>-5.352802846647599</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-6.814862367594323</v>
+        <v>-6.186579877256186</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.145453322826832</v>
+        <v>-5.491636982864797</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-5.532604236988448</v>
+        <v>-4.847778108053795</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.169877434294072</v>
+        <v>-2.850309602431473</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.137563437066603</v>
+        <v>-2.794145449486443</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.03307064452583575</v>
+        <v>0.116515016257857</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.013217347240406</v>
+        <v>-1.841218587673822</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001831</t>
+          <t>X ≈ -0.001821</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.151262475451524</v>
+        <v>-6.680474857462336</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.953731919805378</v>
+        <v>-3.17394793331799</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.628538914259671</v>
+        <v>-4.85373786563968</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.781141977629993</v>
+        <v>-5.688412868721372</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.756803296575882</v>
+        <v>-3.62355438012203</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.139126232820381</v>
+        <v>-2.858438776106468</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.224744485774679</v>
+        <v>-2.604311434992425</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.655791203471757</v>
+        <v>-4.172941942029915</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.36133688644901</v>
+        <v>-4.988084742094877</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-5.89212910323964</v>
+        <v>-5.62635535269488</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-7.38590802956039</v>
+        <v>-7.11376759111495</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.999055596016582</v>
+        <v>-7.700392424993574</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.454576224249607</v>
+        <v>-7.138850415127465</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.228840574023074</v>
+        <v>-6.894008934581585</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -2.555e-05</t>
+          <t>X ≈ -1.65e-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.303411532010045</v>
+        <v>2.241280688738215</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1164283742925534</v>
+        <v>0.1051246511770998</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.052834804231445</v>
+        <v>-0.8397884196381256</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.6486319820890429</v>
+        <v>-0.4412901875451283</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.191393139125132</v>
+        <v>-4.323799180387226</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.43662148077668</v>
+        <v>-0.7796153496476066</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9751258260402906</v>
+        <v>-0.9596889467442651</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.715551272851918</v>
+        <v>-1.699420927478464</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.230887066651711</v>
+        <v>-1.464202897966594</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.1079308979973064</v>
+        <v>0.1655674092885988</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1755478136902795</v>
+        <v>0.1253611000943664</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.577652328046376</v>
+        <v>1.546219920732369</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.705446680212418</v>
+        <v>1.422796484461607</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.75310013865807</v>
+        <v>2.7634101490668</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.00178</t>
+          <t>X ≈ 0.001788</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.159934672859123</v>
+        <v>-2.034354208777103</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.885250868165386</v>
+        <v>-2.349549450640524</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5459680878213433</v>
+        <v>0.4323470414048387</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.932839211908245</v>
+        <v>1.832996670963006</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.080339500821346</v>
+        <v>1.024757966529762</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4.836736184496971</v>
+        <v>4.160161385615119</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.864778163663964</v>
+        <v>2.50795263339549</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.915266392841737</v>
+        <v>4.902740623624346</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.538929225496631</v>
+        <v>4.864669582177761</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>6.208115277003486</v>
+        <v>6.265080344735736</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>6.948136771428047</v>
+        <v>7.013514858404214</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>8.122745452803166</v>
+        <v>7.902228308982011</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7.071679772991409</v>
+        <v>7.19065689574456</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>6.666500596719516</v>
+        <v>6.485870209628622</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.003586</t>
+          <t>X ≈ 0.003592</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.778895786527059</v>
+        <v>-1.663789279548546</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.9963017635499227</v>
+        <v>-0.8753572664804281</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.387531129991309</v>
+        <v>-1.272100348027188</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.257142238193452</v>
+        <v>-1.291091336539765</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.591682336273017</v>
+        <v>0.5980270037275943</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.933800757691252</v>
+        <v>2.908065115132004</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.242843956766244</v>
+        <v>5.226295960660721</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>6.146020252780303</v>
+        <v>6.120161097409394</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7.797885953294866</v>
+        <v>7.782356337844377</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>7.2936948554661</v>
+        <v>7.299642645663226</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.09121938117044</v>
+        <v>7.096714256375172</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.440666026676446</v>
+        <v>6.474988757379428</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.047912433637016</v>
+        <v>7.101198262172247</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>8.985976850986823</v>
+        <v>9.053139155423459</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.005391</t>
+          <t>X ≈ 0.005396</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.3638446404403055</v>
+        <v>0.3576408360047836</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.011454305968208</v>
+        <v>0.8231140594034372</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.6184441296430023</v>
+        <v>0.4255896430210839</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.290379371059657</v>
+        <v>-1.501967281712581</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.248029625438484</v>
+        <v>2.119684895064729</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.137219379105616</v>
+        <v>1.98435403504763</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.051655152804258</v>
+        <v>1.921590561851126</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.855383906658922</v>
+        <v>4.742933440739073</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.432565174153247</v>
+        <v>6.349197420576182</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.219877464956468</v>
+        <v>7.166263890989342</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.439973030395684</v>
+        <v>6.547684912704149</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>9.753039707341124</v>
+        <v>9.896305442184222</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>11.38206918189661</v>
+        <v>11.39216173151066</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>12.01764089769687</v>
+        <v>12.05977390809004</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.007196</t>
+          <t>X ≈ 0.007201</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.629138234449492</v>
+        <v>2.964454517094708</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.27539579319545</v>
+        <v>2.637551988545475</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4855640004358364</v>
+        <v>-0.4910702261207405</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.90016008251974</v>
+        <v>2.600439501415238</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.752688261981049</v>
+        <v>1.266343738357833</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.456627699535055</v>
+        <v>3.662249333567345</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.618670018969873</v>
+        <v>3.598236237896437</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.858232727802623</v>
+        <v>1.860844036118905</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.798045169572099</v>
+        <v>1.823125425549755</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.814215030327873</v>
+        <v>1.842278463259561</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.505617768171518</v>
+        <v>5.44610232701487</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.643892024423046</v>
+        <v>1.695558751655966</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.955342902711322</v>
+        <v>2.997181082910274</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.882377254236602</v>
+        <v>2.221592977630372</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.009002</t>
+          <t>X ≈ 0.009005</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.5122913887005609</v>
+        <v>-0.5366458215702252</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.141051502776776</v>
+        <v>-3.34702025332642</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.557694902813601</v>
+        <v>-1.750708490397336</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.429356101154532</v>
+        <v>-3.610874200426444</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.964326647564477</v>
+        <v>-3.105098465756477</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.147215273134748</v>
+        <v>-5.319875135992298</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.243343970509827</v>
+        <v>-3.390481473974006</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.431050359939846</v>
+        <v>-1.866264483113547</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.998743756041705</v>
+        <v>-1.405724654439311</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.4397561558689631</v>
+        <v>-0.2395034840106192</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.7649450023911726</v>
+        <v>-1.438668807168483</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.2305668500358706</v>
+        <v>-0.8829896319926789</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.150717703349287</v>
+        <v>-3.765709747611254</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.924982053122783</v>
+        <v>-2.521640009974035</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2074880154490089</v>
+        <v>0.1844989535561368</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.794182268986461</v>
+        <v>2.792938634867312</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.397650260072901</v>
+        <v>5.393212622600501</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.532156136909407</v>
+        <v>8.517108639863089</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.795088664112029</v>
+        <v>6.830254708492042</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.078722920902138</v>
+        <v>1.115016275215162</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2151219707629437</v>
+        <v>-0.1432446044294622</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6821906145496826</v>
+        <v>-0.6090773648128049</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.2113616991867673</v>
+        <v>-0.04724757874004837</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.445786012805641</v>
+        <v>-2.667483345183712</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.445667893957427</v>
+        <v>-1.674019002300675</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.616109018710574</v>
+        <v>-2.81345705535491</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.433850233469769</v>
+        <v>-2.609812586709182</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-4.015343498905857</v>
+        <v>-4.15717491032256</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>132</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.822114272495945</v>
+        <v>2.792918478143314</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.726079694583653</v>
+        <v>2.724892908138997</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.119187097707432</v>
+        <v>6.11903370770311</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.522139514023067</v>
+        <v>8.521645021645064</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7.983849960927323</v>
+        <v>8.032395880693095</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.250920960259386</v>
+        <v>5.274878369208999</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.408634843417502</v>
+        <v>4.456646522407823</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.941566199630763</v>
+        <v>3.99081376202448</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.422446259922296</v>
+        <v>-1.3491891501426</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7572135411007466</v>
+        <v>-0.6578662158061732</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.719490456936661</v>
+        <v>-1.619582420917986</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.442688062157046</v>
+        <v>-2.318991441128802</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.9250398724082913</v>
+        <v>1.073729420186119</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>94</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.157381841806043</v>
+        <v>8.128186047453411</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>11.86534468491249</v>
+        <v>11.86415789846783</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>12.53440308739146</v>
+        <v>12.53424969738714</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.53696865651174</v>
+        <v>10.53647416413374</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>12.12633867788413</v>
+        <v>12.1748845976499</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.23222334581709</v>
+        <v>9.256180754766703</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.147512986550922</v>
+        <v>9.195524665541242</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.425125193828009</v>
+        <v>4.474372756221726</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.236483462837121</v>
+        <v>2.309740572616818</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.578054028209422</v>
+        <v>4.677401353503996</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.30952308271516</v>
+        <v>3.409431118733835</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.343901235070447</v>
+        <v>3.467597856098692</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.051409956225179</v>
+        <v>5.200099504003006</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>5.277145606451711</v>
+        <v>5.449144366018373</v>
       </c>
     </row>
     <row r="30">
@@ -1823,98 +1823,98 @@
         <v>85</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.69555455770098</v>
+        <v>8.666358763348349</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.378486111695928</v>
+        <v>2.377299325251272</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.689597079882077</v>
+        <v>6.689443689877756</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.996292811705743</v>
+        <v>7.99579831932774</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.752120905668846</v>
+        <v>2.800666825434618</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.87302434706865</v>
+        <v>1.896981756018263</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.964784576037772</v>
+        <v>3.012796255028093</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.966145540434148</v>
+        <v>6.039402650213844</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.292697332339579</v>
+        <v>6.392044657634152</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.440937350550044</v>
+        <v>8.540845386568719</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.651786091140558</v>
+        <v>9.775482712168802</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.055164649591887</v>
+        <v>8.203854197369715</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.927959123347833</v>
+        <v>6.099957882914495</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.01803</t>
+          <t>X ≈ 0.01802</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>52</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.5578391074574256</v>
+        <v>-0.5870349018100569</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.677128645632592</v>
+        <v>1.675941859187937</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.97466495318524</v>
+        <v>8.974511563180918</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>12.95104394292742</v>
+        <v>12.95054945054942</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.48967746675485</v>
+        <v>10.53822338652062</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>18.4793591886976</v>
+        <v>18.50331659764721</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.47157190635453</v>
+        <v>16.51958358534485</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.15834941641393</v>
+        <v>12.20759697880765</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>14.02044418296808</v>
+        <v>14.09370129274777</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>17.01667923279206</v>
+        <v>17.11602655808663</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.96582422837795</v>
+        <v>13.06573226439663</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>16.84635622688723</v>
+        <v>16.97005284791548</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.58005152741994</v>
+        <v>12.72874107519777</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.036556408415706</v>
+        <v>7.208555167982368</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>44</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.026370575988899</v>
+        <v>-7.055566370341531</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>11.81698878549275</v>
+        <v>11.8158019990481</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>15.96767194619223</v>
+        <v>15.96751855618791</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.734260726144214</v>
+        <v>4.733766233766211</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.622210645133279</v>
+        <v>-2.573664725367507</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.493345202683606</v>
+        <v>4.51730261163322</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.681362116144761</v>
+        <v>6.729373795135082</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.214293472357959</v>
+        <v>6.263541034751675</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.426038588562484</v>
+        <v>8.499295698342181</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.848847064959898</v>
+        <v>9.948194390254471</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.644145906699734</v>
+        <v>9.744053942718409</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.860342240873251</v>
+        <v>2.984038861901496</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.440191387559807</v>
+        <v>2.588880935337635</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.393199765059066</v>
+        <v>0.5651985246257283</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>21</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-14.38567793529626</v>
+        <v>-14.41487372964889</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-11.23495926645528</v>
+        <v>-11.23614605289994</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.62973065121037</v>
+        <v>-11.62988404121469</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.786208778092316</v>
+        <v>2.785714285714313</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.009823986901353</v>
+        <v>7.058369906667124</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-2.216611507273051</v>
+        <v>-2.192654098323437</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-2.301321866539318</v>
+        <v>-2.253310187548998</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.768390510325922</v>
+        <v>-2.719142947932205</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.694436856960756</v>
+        <v>6.767693966740453</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>15.16362642618023</v>
+        <v>15.2635344621989</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.19800457853548</v>
+        <v>15.32170119956373</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.4921394395078877</v>
+        <v>0.6408289872857154</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.02345</t>
+          <t>X ≈ 0.02344</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-15.63881076737646</v>
+        <v>-13.62122293599809</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.723681070966606</v>
+        <v>-9.648844465598394</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-12.38161035045844</v>
+        <v>-10.0425824539131</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.538088477340438</v>
+        <v>6.753968253968253</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.263358970492092</v>
+        <v>0.7091635574607764</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.29717295387983</v>
+        <v>6.537504631835262</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-2.050695300123216</v>
+        <v>0.9212929870542439</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.745393950826895</v>
+        <v>6.011015782226458</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.684411794304118</v>
+        <v>5.974043173089662</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.097650892711094</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-3.633366055022741</v>
+        <v>-0.6094814108169686</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.927327886806303</v>
+        <v>10.55979643765911</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-4.019138755980869</v>
+        <v>-0.9464726000159445</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-3.793403105754336</v>
+        <v>-0.6974277380005347</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1145 +2210,1145 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02801</t>
+          <t>X &gt; -0.02798</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4095</v>
+        <v>4105</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2413834112549011</v>
+        <v>-0.2274503387286515</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.06239674254144489</v>
+        <v>-0.04908196323690817</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2248179798583294</v>
+        <v>-0.235326218085433</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3737007399171119</v>
+        <v>-0.3838743273737251</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3384077034356068</v>
+        <v>-0.3495519397573972</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2714610366534416</v>
+        <v>-0.2823349013521934</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2210358272088442</v>
+        <v>-0.2325115957386714</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2359071438996807</v>
+        <v>-0.2472614685100538</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2103250478011418</v>
+        <v>-0.222226088873029</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2173553347384782</v>
+        <v>-0.2052382078118526</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1400060077596805</v>
+        <v>-0.1280359926626886</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1651531326817164</v>
+        <v>-0.153619681162489</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.03450676584928658</v>
+        <v>-0.02370375225923027</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.01472564286634537</v>
+        <v>-0.004505827051829669</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02621</t>
+          <t>X &gt; -0.02618</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4073</v>
+        <v>4084</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1803776066479088</v>
+        <v>-0.1791379415577126</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1141339473435963</v>
+        <v>-0.1137967225428369</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.250830413348325</v>
+        <v>-0.2501526614833054</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.4012234321172912</v>
+        <v>-0.4001325982273798</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3873436013490448</v>
+        <v>-0.3875598456393661</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3216511217466618</v>
+        <v>-0.3214070657861186</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2459997376877183</v>
+        <v>-0.2465822947296132</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2584382577897699</v>
+        <v>-0.2590195342636221</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2078728653587731</v>
+        <v>-0.2092127166959443</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2348820585043256</v>
+        <v>-0.236826068738587</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1314808218220165</v>
+        <v>-0.1337181506152447</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1569472181340359</v>
+        <v>-0.1597336651309789</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.04787037885247969</v>
+        <v>-0.05159975899863412</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.004653057296579277</v>
+        <v>-0.009104743115351255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.0244</t>
+          <t>X &gt; -0.02437</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4054</v>
+        <v>4064</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2556885901606094</v>
+        <v>-0.2658145474771274</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2308133877398433</v>
+        <v>-0.2414734046453901</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.341732056938703</v>
+        <v>-0.3520575732041706</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.4688530891743028</v>
+        <v>-0.4788905252822815</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.403183056920362</v>
+        <v>-0.3902171883722119</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3139597523318187</v>
+        <v>-0.3005219999045394</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2621806744800566</v>
+        <v>-0.2495904977570262</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2724956006379742</v>
+        <v>-0.2598004885898106</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2214115223022546</v>
+        <v>-0.2341433865345977</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2445710989363334</v>
+        <v>-0.2578483379121508</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1643780810207218</v>
+        <v>-0.1778228035989784</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2394425896808485</v>
+        <v>-0.2534516357956349</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.152567271783326</v>
+        <v>-0.1674648099379965</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1102311897779131</v>
+        <v>-0.1260147896190915</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.02259</t>
+          <t>X &gt; -0.02257</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4036</v>
+        <v>4047</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1964013355479324</v>
+        <v>-0.1948408889263931</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2877542975112277</v>
+        <v>-0.2869326646621957</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3480052108488891</v>
+        <v>-0.3470564695748948</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5009884537416198</v>
+        <v>-0.4996126624176966</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4573606619890995</v>
+        <v>-0.4578318403038608</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3938052334282389</v>
+        <v>-0.3935818183634012</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3167041262945105</v>
+        <v>-0.3175383455116716</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.3002582796999462</v>
+        <v>-0.3011809444780411</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2239355402535068</v>
+        <v>-0.2259129528289492</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2681646362102086</v>
+        <v>-0.2709434208359482</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.186707814968571</v>
+        <v>-0.1897283243972154</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3365599159100725</v>
+        <v>-0.3400142151770567</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2722188180384109</v>
+        <v>-0.2767317128837163</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2307303187322631</v>
+        <v>-0.2361807237513034</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.02079</t>
+          <t>X &gt; -0.02077</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4011</v>
+        <v>4022</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1946337243713288</v>
+        <v>-0.192887537402477</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2765415966282632</v>
+        <v>-0.2757380919962387</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3098471533059808</v>
+        <v>-0.30899565610612</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4148428437501863</v>
+        <v>-0.4136904761904745</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3924503556714996</v>
+        <v>-0.3934026654229825</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2556877996462248</v>
+        <v>-0.2559886132708868</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2024335307171157</v>
+        <v>-0.2038828216658715</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1829500608078689</v>
+        <v>-0.1845044649323242</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1804445697135009</v>
+        <v>-0.1830078436584088</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2445526859740994</v>
+        <v>-0.2480301502323599</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1363949276527876</v>
+        <v>-0.1401922458756317</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2624631869409413</v>
+        <v>-0.2669099904390464</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.2200098269783979</v>
+        <v>-0.2256175167447125</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1547252593057422</v>
+        <v>-0.1614865257788622</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01898</t>
+          <t>X &gt; -0.01896</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3964</v>
+        <v>3974</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2053314190181297</v>
+        <v>-0.2151532093866066</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2188626869784684</v>
+        <v>-0.2297665818943173</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3736659611834128</v>
+        <v>-0.3841410765256725</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5569503275227845</v>
+        <v>-0.5418818129661531</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4776210288597937</v>
+        <v>-0.4903789426089631</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2924279365638327</v>
+        <v>-0.3043950277439578</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1871848493551482</v>
+        <v>-0.2007031613171861</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.212315183469812</v>
+        <v>-0.2257234695881749</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.2090652846366226</v>
+        <v>-0.2237731403335914</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1882680376793928</v>
+        <v>-0.2042348798218541</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.07638941882679973</v>
+        <v>-0.09262057210549557</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.179129633696995</v>
+        <v>-0.1964074523476711</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1816130375233129</v>
+        <v>-0.2001413631186324</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.04254007532255599</v>
+        <v>-0.06274675606238134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01718</t>
+          <t>X &gt; -0.01716</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3907</v>
+        <v>3918</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1084670509425152</v>
+        <v>-0.1061433690233358</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1752866094364052</v>
+        <v>-0.1747138464296114</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1479250652700159</v>
+        <v>-0.1475003012590435</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5144221712494144</v>
+        <v>-0.5129473377945928</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5027009413539147</v>
+        <v>-0.5046553034169108</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.319147540843602</v>
+        <v>-0.3199131527348413</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3133422086566853</v>
+        <v>-0.3157912309216897</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2553996252420774</v>
+        <v>-0.2580973676206355</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.2512248433021682</v>
+        <v>-0.2555996739378443</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.192179410482332</v>
+        <v>-0.1985303791118085</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1268375855114101</v>
+        <v>-0.1334123808076129</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1548441588104978</v>
+        <v>-0.1629926779872264</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.151229474075997</v>
+        <v>-0.1611248639154255</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.09019833159728563</v>
+        <v>-0.1018857948322562</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01537</t>
+          <t>X &gt; -0.01535</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3822</v>
+        <v>3833</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.06892124565821689</v>
+        <v>-0.06601406097642837</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1797390563055359</v>
+        <v>-0.1791146577671583</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.221285196326086</v>
+        <v>-0.2206377204178978</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5727235213410538</v>
+        <v>-0.5710382513661187</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6271227260046359</v>
+        <v>-0.6298381199063385</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4461278568938738</v>
+        <v>-0.4470769296793975</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3338804109808038</v>
+        <v>-0.3373875685013132</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2381621180286402</v>
+        <v>-0.2420593820234913</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.02876562374314062</v>
+        <v>0.0218690083047548</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.08194120552921191</v>
+        <v>0.07246287652452565</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1272118603539028</v>
+        <v>0.1175490607390444</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.09788503280930883</v>
+        <v>0.0860893537824623</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.03251535969020836</v>
+        <v>0.01857695658294745</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.08993160464805072</v>
+        <v>0.07365380532207411</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01357</t>
+          <t>X &gt; -0.01355</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3747</v>
+        <v>3757</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.03410751989605387</v>
+        <v>-0.01674312462173333</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2479946482057898</v>
+        <v>-0.2328484749141637</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3357292827012799</v>
+        <v>-0.3203602316908771</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.6968133900509841</v>
+        <v>-0.680477075353636</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6617110807998543</v>
+        <v>-0.6509591781266408</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5096810653226669</v>
+        <v>-0.4965812468721325</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2336860748757559</v>
+        <v>-0.2240606556426528</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1266943434499694</v>
+        <v>-0.1173687809176158</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.01355554921377689</v>
+        <v>0.0197635345994982</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1914223782097011</v>
+        <v>0.1943813327987627</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2683883309421375</v>
+        <v>0.2711332463934326</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2644985007243221</v>
+        <v>0.2645051367811462</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1795917950498591</v>
+        <v>0.177056463906986</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.1803021742591469</v>
+        <v>0.1750177711231728</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.01176</t>
+          <t>X &gt; -0.01174</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3650</v>
+        <v>3661</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2832638328821488</v>
+        <v>-0.2782119881967304</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4055920198297471</v>
+        <v>-0.4042064161686199</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5671794356954791</v>
+        <v>-0.5654582709065608</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7500909877156801</v>
+        <v>-0.7477721134762874</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7271325065459919</v>
+        <v>-0.7319505812010476</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4149504382528022</v>
+        <v>-0.417160581210986</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1567068425148719</v>
+        <v>-0.163161150835009</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.007110943794785385</v>
+        <v>-0.01419404718298978</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1111523803794299</v>
+        <v>0.1002479375922931</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3984315800616542</v>
+        <v>0.3828961141785783</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5103082141431585</v>
+        <v>0.4943516799156882</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5602327118480233</v>
+        <v>0.5406864185490221</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5664830635638936</v>
+        <v>0.5433022649637635</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5065247961923163</v>
+        <v>0.5074646714807827</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.009956</t>
+          <t>X &gt; -0.00994</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3552</v>
+        <v>3560</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1948010235217268</v>
+        <v>-0.2011277778676686</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.2481066129359988</v>
+        <v>-0.2858980925736319</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4593685967618697</v>
+        <v>-0.4405413200881512</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5666427499417281</v>
+        <v>-0.5756302521008436</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.7528430007024483</v>
+        <v>-0.7135816870832912</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4683504050793985</v>
+        <v>-0.4536513223251788</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.2006782935719968</v>
+        <v>-0.1907526161604096</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.006003936809570121</v>
+        <v>0.003662382837156031</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.08908456704282486</v>
+        <v>0.06629812088458209</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3795761783661789</v>
+        <v>0.3522347942948798</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5845627331924845</v>
+        <v>0.5568266317189696</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6912114279607451</v>
+        <v>0.6870657620086504</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6811145510835814</v>
+        <v>0.6729227009295258</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.55699992885922</v>
+        <v>0.5728594030731244</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.00815</t>
+          <t>X &gt; -0.008136</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3387</v>
+        <v>3397</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.06915132465199747</v>
+        <v>-0.07609422957906986</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.01737426246255325</v>
+        <v>-0.03051390270930909</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1902284230089037</v>
+        <v>-0.1736466166674049</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3089592272906145</v>
+        <v>-0.2919828923644658</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4485303795802267</v>
+        <v>-0.4423990444835155</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1645741975038177</v>
+        <v>-0.1536358478514757</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1792460825024733</v>
+        <v>0.183598771099156</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3472677777460902</v>
+        <v>0.3215914181032957</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4205711786139474</v>
+        <v>0.3890931436951846</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7961407032001659</v>
+        <v>0.7577156540538894</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9621936406766451</v>
+        <v>0.9231983277451263</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.101979623850227</v>
+        <v>1.057001497970887</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.200521966072195</v>
+        <v>1.149531585452671</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.118566810178102</v>
+        <v>1.091732632260808</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.006345</t>
+          <t>X &gt; -0.006331</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3181</v>
+        <v>3190</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.07154247244091039</v>
+        <v>0.06559844673337523</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.3327036273575743</v>
+        <v>-0.3456311961140415</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3032320166578302</v>
+        <v>-0.3164552020126479</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2814132550469921</v>
+        <v>-0.2946428571428612</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5518836688796824</v>
+        <v>-0.5794335735871172</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.01347751704430067</v>
+        <v>-0.008253133434699578</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5106971990097833</v>
+        <v>0.4799069654367472</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6573112204604925</v>
+        <v>0.6258120553456337</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.9592196931721588</v>
+        <v>0.9192700901475632</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.446037562904166</v>
+        <v>1.427957582603767</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.730656631287715</v>
+        <v>1.711568107225972</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.971821584910693</v>
+        <v>1.944508217107654</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.104390753110948</v>
+        <v>2.068952728164042</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.015759851938547</v>
+        <v>2.022878775409431</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.004539</t>
+          <t>X &gt; -0.004527</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2929</v>
+        <v>2936</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.08377220190462964</v>
+        <v>-0.05165132980390297</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1805374977478422</v>
+        <v>-0.1584178109926313</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.0806128754849027</v>
+        <v>-0.05879479791641273</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1021671559975701</v>
+        <v>0.123508874018043</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.008999885855111245</v>
+        <v>-0.0076823206754284</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.6817276649080455</v>
+        <v>0.6913391728980613</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.024710420310747</v>
+        <v>1.023229786238744</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.121959085545079</v>
+        <v>1.120162998783591</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.489299909580375</v>
+        <v>1.476328865786769</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.95476297715139</v>
+        <v>1.930259943748602</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.452216375977954</v>
+        <v>2.392295459622709</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.472504822319067</v>
+        <v>2.402319696111498</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.584516164865121</v>
+        <v>2.5037600636999</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.434697018232654</v>
+        <v>2.398242864482057</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.002734</t>
+          <t>X &gt; -0.002723</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2657</v>
+        <v>2664</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3070029870560944</v>
+        <v>-0.3248297927614701</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.08862528547568616</v>
+        <v>0.05469315273742836</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3518361690661322</v>
+        <v>0.3167114193994678</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8028263069049402</v>
+        <v>0.7662677636499637</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.5104674875448509</v>
+        <v>0.4472855178049642</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.354370020899587</v>
+        <v>1.302142023718162</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.741467300216861</v>
+        <v>1.674236121128033</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.934460190269917</v>
+        <v>1.866196805946807</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.270877959717652</v>
+        <v>2.187772826309754</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.721252959178507</v>
+        <v>2.622311876965668</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.027756276766056</v>
+        <v>2.927576456949559</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.046813654292315</v>
+        <v>2.932889710977356</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.852481393376351</v>
+        <v>2.747502801276568</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.890034883271674</v>
+        <v>2.831100790527998</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0009283</t>
+          <t>X &gt; -0.0009186</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2346</v>
+        <v>2352</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4677475248326388</v>
+        <v>0.5182659811274206</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4919386234306771</v>
+        <v>0.4829822763978342</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.01206492052151</v>
+        <v>1.002587344965896</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.675637106772953</v>
+        <v>1.62250090876045</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.076162804621383</v>
+        <v>0.9872948920197757</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.950055159393578</v>
+        <v>1.854055803286734</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.399818479007735</v>
+        <v>2.241798552041985</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.808103917232266</v>
+        <v>2.667307048025357</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.2826506865539</v>
+        <v>3.139672299669549</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.863095167794036</v>
+        <v>3.716522836002277</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.408254827178467</v>
+        <v>4.25959148373363</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.511121129503763</v>
+        <v>4.343427137177578</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.218847514042025</v>
+        <v>4.058957819779152</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.231454434515776</v>
+        <v>4.121166366307847</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0008772</t>
+          <t>X &gt; 0.0008856</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1981</v>
+        <v>1986</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1295257365339211</v>
+        <v>0.2007315486069956</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6040304730869082</v>
+        <v>0.5526176695654001</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.392523476571405</v>
+        <v>1.342118830285671</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.103884566356307</v>
+        <v>2.002837032248792</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.046711981535822</v>
+        <v>1.966076579079676</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.574051612529438</v>
+        <v>2.339415139628116</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.021653244955495</v>
+        <v>2.831800779914971</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.641589098646058</v>
+        <v>3.472051478556274</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.114271726392403</v>
+        <v>3.988120598931793</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.55498560619678</v>
+        <v>4.370928518870954</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>5.188132696902443</v>
+        <v>5.021488926035722</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>5.051613866773806</v>
+        <v>4.85892453960404</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.681942569240313</v>
+        <v>4.544776071907151</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.503841773227578</v>
+        <v>4.371387300603025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.002683</t>
+          <t>X &gt; 0.00269</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1664</v>
+        <v>1672</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.5656789515444984</v>
+        <v>0.6204785150056864</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.078250536294227</v>
+        <v>1.097641877546664</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.553796348106118</v>
+        <v>1.512973101642466</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.136469528712105</v>
+        <v>2.0347328895716</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.230810585133462</v>
+        <v>2.142855313733179</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.142999323278424</v>
+        <v>1.997480736972655</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.051538702148648</v>
+        <v>2.892619151928798</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.398947450653246</v>
+        <v>3.203369426193007</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.03337243119045</v>
+        <v>3.823505538681054</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.240056456169292</v>
+        <v>4.015208618559029</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.852843459147259</v>
+        <v>4.647388362181836</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.466548534579509</v>
+        <v>4.287395003967276</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.22668614280456</v>
+        <v>4.047882185133858</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.091844869954173</v>
+        <v>3.974289433716635</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.004488</t>
+          <t>X &gt; 0.004494</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.064670076556816</v>
+        <v>1.107833182348905</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.51977332897242</v>
+        <v>1.518586542527764</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.179793158313444</v>
+        <v>2.107176000193185</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.858725094263427</v>
+        <v>2.744306418219452</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.579662952966736</v>
+        <v>2.47244858161536</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.974694644817383</v>
+        <v>1.803205114927053</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.585167612973486</v>
+        <v>2.394722938745062</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.814293472357988</v>
+        <v>2.581064091405196</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.232178591209042</v>
+        <v>2.978874090964062</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.590156738534688</v>
+        <v>3.314465800004136</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.37645441451842</v>
+        <v>4.124818106091247</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.046401079993281</v>
+        <v>3.820666002876429</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.626250226679872</v>
+        <v>3.396449001788952</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.050236605769371</v>
+        <v>2.890703208620984</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.006294</t>
+          <t>X &gt; 0.006298</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.216267068057199</v>
+        <v>1.268447050332703</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.629728862317307</v>
+        <v>1.667485056535874</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.517531777990385</v>
+        <v>2.467198453755131</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.756226414776584</v>
+        <v>3.653420523138827</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.651399240127098</v>
+        <v>2.547974199088323</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.939538585272771</v>
+        <v>1.764421689738235</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.700572790527815</v>
+        <v>2.496019121639534</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.372781002526935</v>
+        <v>2.118214530270272</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.539896387096995</v>
+        <v>2.257298259161651</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.805004382819341</v>
+        <v>2.489807706515677</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.930090458601704</v>
+        <v>3.606089794190851</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.81198634145349</v>
+        <v>2.519890334372654</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.948573076792556</v>
+        <v>1.684591562738404</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.110478939785054</v>
+        <v>0.9276334465320133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.008099</t>
+          <t>X &gt; 0.008103</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.8524173027989832</v>
+        <v>0.8232215084463519</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.463453431957376</v>
+        <v>1.412828998744708</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.290904269424551</v>
+        <v>3.243785114990622</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.929842682345459</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.882839859917219</v>
+        <v>2.884420015253383</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.29132500066342</v>
+        <v>1.266215545195777</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.206614641397252</v>
+        <v>2.206671803022594</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.247765006385698</v>
+        <v>2.185777863551387</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.473416600305754</v>
+        <v>2.371274664870654</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.802632410049597</v>
+        <v>2.659793136335971</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.26682757285964</v>
+        <v>3.123060920168079</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.855274844501466</v>
+        <v>2.736288836620851</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.431779509582711</v>
+        <v>1.34001856300474</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.6541706782038901</v>
+        <v>0.5879510779678156</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.009905</t>
+          <t>X &gt; 0.009907</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.244012336227826</v>
+        <v>1.214816541875194</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.784688707347378</v>
+        <v>2.783501920902722</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.682180932907528</v>
+        <v>4.682027542903207</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.101804357298178</v>
+        <v>6.101309864920175</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.56064947468959</v>
+        <v>4.609195394455362</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.138825796588286</v>
+        <v>3.162783205537899</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.770447815545623</v>
+        <v>3.818459494535944</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.303379171758884</v>
+        <v>3.352626734152601</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.469732341008033</v>
+        <v>3.458920600660498</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.480645682411321</v>
+        <v>3.494690873713708</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.423720707795319</v>
+        <v>4.436682231335212</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.740738745373022</v>
+        <v>3.778516590476613</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.746699800237515</v>
+        <v>2.81029276133399</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.394243197953294</v>
+        <v>1.48340639125766</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>531</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.568048187921391</v>
+        <v>1.53885239356876</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.781720851919715</v>
+        <v>2.780534065475059</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.458512555676919</v>
+        <v>4.458359165672597</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.342033367815183</v>
+        <v>5.34153887543718</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.862124229032105</v>
+        <v>3.910670148797877</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.782850424392237</v>
+        <v>3.80680783334185</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.016407485088408</v>
+        <v>5.064419164078728</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.549338841301669</v>
+        <v>4.598586403695386</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.488356684778893</v>
+        <v>4.561613794558589</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.333353142686313</v>
+        <v>5.432700467980887</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.258595487250979</v>
+        <v>6.358503523269654</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.72800188819388</v>
+        <v>5.851698509222125</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.366231449193087</v>
+        <v>4.514920996970915</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.085375762319806</v>
+        <v>3.257374521886469</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>399</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.153169182498225</v>
+        <v>1.123973388145593</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.800128452842927</v>
+        <v>2.798941666398271</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.909116466584123</v>
+        <v>3.908963076579802</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.289968176588523</v>
+        <v>4.28947368421052</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.498545791412631</v>
+        <v>2.547091711178403</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>3.321130362829415</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.217475125941952</v>
+        <v>5.265486804932273</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.750406482155213</v>
+        <v>4.79965404454893</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.443810290544711</v>
+        <v>6.517067400324407</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.348277459127139</v>
+        <v>7.447624784421713</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.897962265779228</v>
+        <v>8.997870301797903</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.431087285302461</v>
+        <v>8.554783906330705</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.504670767828657</v>
+        <v>5.653360315606484</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.72790015239103</v>
+        <v>4.899898911957692</v>
       </c>
     </row>
     <row r="30">
@@ -3465,98 +3465,98 @@
         <v>305</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.005506194468772</v>
+        <v>-1.034701988821404</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.006258532139526096</v>
+        <v>0.005071745694870344</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.250831409679563</v>
+        <v>1.250678019675242</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.364663110644983</v>
+        <v>2.36416861826698</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.468708409663833</v>
+        <v>-0.4201624898980612</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.468009882266337</v>
+        <v>1.49196729121595</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.006250342672303</v>
+        <v>4.054262021662623</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.740494624330005</v>
+        <v>7.813751734109701</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.202051237836201</v>
+        <v>8.301398563130775</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>10.62030089924815</v>
+        <v>10.72020893526683</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.998941346685434</v>
+        <v>10.12263796771368</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.644364263863828</v>
+        <v>5.793053811641656</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.55862450425429</v>
+        <v>4.730623263820952</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01713</t>
+          <t>X &gt; 0.01712</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>220</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.753643303261626</v>
+        <v>-4.782839097614257</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.9102839417799942</v>
+        <v>-0.9114707282246499</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8505098719895798</v>
+        <v>-0.8506632619939012</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1888061806896815</v>
+        <v>0.1883116883116784</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.713119736042366</v>
+        <v>-1.664573816276594</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.311527020865441</v>
+        <v>1.335484429815054</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.40863484341746</v>
+        <v>4.45664652240778</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.426038588562484</v>
+        <v>8.499295698342181</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.939756155868992</v>
+        <v>9.039103481163565</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>11.46232772488152</v>
+        <v>11.56223576090019</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.1330695136005</v>
+        <v>10.25676613462874</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.71291866028708</v>
+        <v>4.861608208064908</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.029563401422699</v>
+        <v>4.201562160989361</v>
       </c>
     </row>
     <row r="32">
@@ -3569,98 +3569,98 @@
         <v>168</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-3.891635413115125</v>
+        <v>-3.891788803119447</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.761410269526763</v>
+        <v>-3.761904761904766</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.490176013098647</v>
+        <v>-5.441630093332876</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-4.002325792987371</v>
+        <v>-3.978368384037758</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.6748686096512273</v>
+        <v>0.722880288641548</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.588752346816861</v>
+        <v>2.637999909210578</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.694436856960756</v>
+        <v>6.767693966740453</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.439756155868992</v>
+        <v>6.539103481163565</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.99695975951357</v>
+        <v>11.09686779553225</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.055147435678414</v>
+        <v>8.178844056706659</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.277853725222144</v>
+        <v>2.426543272999972</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.098827470686771</v>
+        <v>3.270826230253434</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.02074</t>
+          <t>X &gt; 0.02073</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>124</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-5.706722482147256</v>
+        <v>-5.735918276499888</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-6.511456962307854</v>
+        <v>-6.51264374875251</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-10.93848641157903</v>
+        <v>-10.93863980158335</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.776003203474531</v>
+        <v>-6.776497695852534</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-6.507841143667001</v>
+        <v>-6.459295223901229</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-7.016918726935138</v>
+        <v>-6.992961317985525</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.456467795878737</v>
+        <v>-1.408456116888416</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.302270011947442</v>
+        <v>1.351517574341159</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.079997532844011</v>
+        <v>6.153254642623708</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.230078736514152</v>
+        <v>5.329426061808725</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.47699048147976</v>
+        <v>11.57689851749844</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9.898465408028635</v>
+        <v>10.02216202905688</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.220250038586201</v>
+        <v>2.368939586364029</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.058888914619182</v>
+        <v>4.230887674185844</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>103</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-3.937226710146</v>
+        <v>-3.966422504498631</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.548412803209828</v>
+        <v>-5.549599589654484</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-10.79755312000371</v>
+        <v>-10.79770651000803</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-8.725580403599807</v>
+        <v>-8.72607489597781</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-9.263869956695501</v>
+        <v>-9.215324036929729</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-7.99562214065265</v>
+        <v>-7.971664731703036</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.28421599506445</v>
+        <v>-1.236204316074129</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.132210506779877</v>
+        <v>2.181458069173594</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.954723495888167</v>
+        <v>6.027980605667864</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.133930913150543</v>
+        <v>4.233278238445116</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.72534625974473</v>
+        <v>10.8252542957634</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.817976839284519</v>
+        <v>8.941673460312764</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.572583267524493</v>
+        <v>2.721272815302321</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.740066490566562</v>
+        <v>4.912065250133224</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.02435</t>
+          <t>X &gt; 0.02434</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-1.290439840058163</v>
+        <v>-1.921876530769339</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-5.282578314074371</v>
+        <v>-4.681524204160482</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-10.43925446073418</v>
+        <v>-10.95761513365166</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-11.499505507622</v>
+        <v>-12.00420168067227</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-10.84731887024151</v>
+        <v>-11.3169802333889</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-10.54994484060642</v>
+        <v>-11.04419471456997</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.110845676063065</v>
+        <v>-1.693086097913074</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>1.37049290640946</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>6.694436856960756</v>
+        <v>6.039402650213844</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>3.463565679678517</v>
+        <v>2.862632892928275</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13.97315023570403</v>
+        <v>13.24672773950982</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>9.245623626154604</v>
+        <v>8.599012123933541</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>4.063568010936422</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>6.670256042115341</v>
+        <v>6.099957882914495</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1145 +3904,1145 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02801</t>
+          <t>X &lt; -0.02798</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11.80479825517994</v>
+        <v>11.01929993981889</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>2.377299325251279</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.98931696783726</v>
+        <v>11.39532604281892</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18.26239925428276</v>
+        <v>18.58403361344537</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>16.53363351071088</v>
+        <v>16.91831388425816</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>13.2595789689174</v>
+        <v>13.66168763837121</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.79391622869885</v>
+        <v>11.24809037267515</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>11.9587282005271</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10.26586542838933</v>
+        <v>10.74528500315501</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>9.921456422340029</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>6.830293092846894</v>
+        <v>6.187904210098061</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.055147435678414</v>
+        <v>7.422541535698244</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1.682615629984049</v>
+        <v>1.145030667957947</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.2176049417380241</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02621</t>
+          <t>X &lt; -0.02618</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>106</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.95304623361659</v>
+        <v>6.923850439263958</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.398463914137665</v>
+        <v>4.397277127693009</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.66406988787319</v>
+        <v>9.663916497868868</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15.45467238995212</v>
+        <v>15.45417789757411</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.91638283685642</v>
+        <v>14.96492875662219</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>12.38356818724623</v>
+        <v>12.40752559619584</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.468669148734776</v>
+        <v>9.516680827725096</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.94499673136314</v>
+        <v>9.994244293756857</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.997222122010172</v>
+        <v>8.070479231789868</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.034095778510505</v>
+        <v>9.133443103805078</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.055809714589927</v>
+        <v>5.155717750608602</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.033584093360346</v>
+        <v>6.157280714388591</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.839848334386559</v>
+        <v>1.988537882164387</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1787915317829061</v>
+        <v>0.3507902913495684</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.0244</t>
+          <t>X &lt; -0.02437</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.319083969465645</v>
+        <v>8.60099928622413</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.50789787640182</v>
+        <v>7.811472994719068</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.11312649164679</v>
+        <v>11.38598897465833</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15.24335163523514</v>
+        <v>15.48412698412697</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.10506208213945</v>
+        <v>12.61392546222269</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>10.20243611177453</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8.517725752508369</v>
+        <v>8.064150129911383</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>8.850657108721627</v>
+        <v>8.391968163178831</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.18967495219885</v>
+        <v>7.561344760391243</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.939756155868992</v>
+        <v>8.324817766877857</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.3350549976088</v>
+        <v>5.739724938389379</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.769433149964122</v>
+        <v>8.178844056706659</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.949282296650715</v>
+        <v>5.402733749190446</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>4.064477023904224</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.02259</t>
+          <t>X &lt; -0.02257</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>143</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.561042011423687</v>
+        <v>5.531846217071056</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.145660114164059</v>
+        <v>8.144473327719403</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.848790827311113</v>
+        <v>9.848637437306792</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>14.17482016670368</v>
+        <v>14.17432567432567</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>12.93722991430729</v>
+        <v>12.98577583407306</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>11.13670184604027</v>
+        <v>11.16065925498988</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.954089388871999</v>
+        <v>9.00210106786232</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8.48702074508526</v>
+        <v>8.536268307478977</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6.328136490660391</v>
+        <v>6.401393600440088</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.576119792232625</v>
+        <v>7.675467117527198</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.273516536070339</v>
+        <v>5.373424572089014</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.503698884229856</v>
+        <v>9.6273955052581</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>7.684946632315047</v>
+        <v>7.833636180092874</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.512080883940186</v>
+        <v>6.684079643506848</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.02079</t>
+          <t>X &lt; -0.02077</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>168</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.622183590687527</v>
+        <v>6.620996804242871</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.417888396408685</v>
+        <v>7.417735006404364</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.929065920949434</v>
+        <v>9.928571428571431</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.390776367853739</v>
+        <v>9.439322287619511</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.116721826060243</v>
+        <v>6.140679235009856</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.841535276317892</v>
+        <v>4.889546955308212</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.374466632531153</v>
+        <v>4.42371419492487</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.844518060630897</v>
+        <v>5.94386538592547</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.258864521418325</v>
+        <v>3.358772557437</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.269433149964122</v>
+        <v>6.393129770992367</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.254044201412619</v>
+        <v>5.402733749190446</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.694065565924859</v>
+        <v>3.866064325491521</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01898</t>
+          <t>X &lt; -0.01896</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.798153736907508</v>
+        <v>3.97136965659449</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.047432760122753</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.908475328856085</v>
+        <v>7.087047175716528</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.29451442593281</v>
+        <v>9.994708994708986</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.825992314697586</v>
+        <v>9.042496890794105</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.402436111774534</v>
+        <v>5.611578705909331</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.4572606362293</v>
+        <v>3.699070764832022</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.920424550582091</v>
+        <v>4.159163930374596</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.859442394059315</v>
+        <v>4.1221913212378</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.474639876799223</v>
+        <v>3.761325703385786</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.409473602259965</v>
+        <v>1.705333403997848</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.304316870894354</v>
+        <v>3.615351993214588</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.683157029613724</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.7843202724586362</v>
+        <v>1.154424113851313</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01718</t>
+          <t>X &lt; -0.01716</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>272</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.563201616524466</v>
+        <v>1.534005822171835</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.525544935225348</v>
+        <v>2.524358148780692</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.130773550470309</v>
+        <v>2.130620160465988</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.408057517588084</v>
+        <v>7.407563025210081</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.237415023315918</v>
+        <v>7.28596094308169</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.593612582362773</v>
+        <v>4.617569991312386</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.508902223096605</v>
+        <v>4.556913902086926</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.674186520486337</v>
+        <v>3.723434082880054</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.613204363963561</v>
+        <v>3.686461473743257</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.763285567633702</v>
+        <v>2.862632892928275</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.823290291726451</v>
+        <v>1.923198327745126</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.225315502905303</v>
+        <v>2.349012123933548</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.172811708415423</v>
+        <v>2.321501256193251</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.295606182171362</v>
+        <v>1.467604941738024</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01537</t>
+          <t>X &lt; -0.01535</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>357</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.7403724848718127</v>
+        <v>0.7111766905191814</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.930306839987253</v>
+        <v>1.929120053542597</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.375871589685993</v>
+        <v>2.375718199681671</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.147553315907409</v>
+        <v>6.147058823529406</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.729711942083426</v>
+        <v>6.778257861849198</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.786189613175097</v>
+        <v>4.81014702212471</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.581031074637224</v>
+        <v>3.629042753627544</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.553738341214618</v>
+        <v>2.602985903608335</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3083642634874195</v>
+        <v>-0.2351071537077232</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.8781710149993529</v>
+        <v>-0.7788236897047796</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.362984218077472</v>
+        <v>-1.263076182058796</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.048494020904222</v>
+        <v>-0.9247973998759775</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.3481966949459263</v>
+        <v>-0.1995071471680987</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.9627971791731724</v>
+        <v>-0.7907984196065101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01357</t>
+          <t>X &lt; -0.01355</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2968617472434261</v>
+        <v>0.1457773206095538</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.157897876401819</v>
+        <v>2.02680346871005</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.920533899054185</v>
+        <v>2.787799891480802</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.060018301901806</v>
+        <v>5.919993401517651</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5.7532102302876</v>
+        <v>5.661691142782821</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.430213889552313</v>
+        <v>4.31784848608212</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.030688715471328</v>
+        <v>1.947723574685753</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.100657108721627</v>
+        <v>1.01999704986823</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1177324552085537</v>
+        <v>-0.1717099703540157</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.662095695982856</v>
+        <v>-1.688379197820268</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.329759817206018</v>
+        <v>-2.354413409790546</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.295381664850694</v>
+        <v>-2.296246672425653</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.558125110756691</v>
+        <v>-1.536670187904022</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.56387094201164</v>
+        <v>-1.518572208105738</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.01176</t>
+          <t>X &lt; -0.01174</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>529</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.961428014834269</v>
+        <v>1.932232220481637</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.807708840484992</v>
+        <v>2.806522054040336</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.925224790323533</v>
+        <v>3.925071400319212</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.189665434857069</v>
+        <v>5.189170942479066</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.029447715409766</v>
+        <v>5.077993635175538</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.869354826330301</v>
+        <v>2.893312235279915</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.083321215646365</v>
+        <v>1.131332894636685</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.04914482138703846</v>
+        <v>0.09839238378075521</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7679810024325278</v>
+        <v>-0.6947238926528314</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.752115299707569</v>
+        <v>-2.652767974412995</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.523924208440349</v>
+        <v>-3.424016172421673</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.867617889733417</v>
+        <v>-3.743921268705172</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.909696909398434</v>
+        <v>-3.761007361620607</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.494925342347713</v>
+        <v>-3.511962499605239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.009956</t>
+          <t>X &lt; -0.00994</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.107600715877133</v>
+        <v>1.140681825906668</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.410290220899427</v>
+        <v>1.620996804242878</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.610415167882827</v>
+        <v>2.497100085769439</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.21910921099272</v>
+        <v>3.261904761904752</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.275715989635465</v>
+        <v>4.042496890794112</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.659214421184416</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.139097363353663</v>
+        <v>1.080023145784402</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.03407018687155272</v>
+        <v>-0.02073024951957336</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.505380869172761</v>
+        <v>-0.3751631761166863</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.15274783137184</v>
+        <v>-1.992642550582467</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.314386788675094</v>
+        <v>-3.149163950499506</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.917967169015142</v>
+        <v>-3.884648006785405</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.859649122807021</v>
+        <v>-3.803615457158756</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.155444573058951</v>
+        <v>-3.237110277683072</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.00815</t>
+          <t>X &lt; -0.008136</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2968617472434261</v>
+        <v>0.3272147829314278</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.07456454306848315</v>
+        <v>0.1311751504867971</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8161567946770774</v>
+        <v>0.7462644005075276</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.325169817053322</v>
+        <v>1.254458656098002</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.923243900321268</v>
+        <v>1.900140158273445</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7054664148048317</v>
+        <v>0.6596848195892164</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.7681328333502222</v>
+        <v>-0.7881087223474665</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.487726729662207</v>
+        <v>-1.380044887522736</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.801234138710242</v>
+        <v>-1.6692243062434</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.40872869261586</v>
+        <v>-3.249673315809957</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.11848035592655</v>
+        <v>-3.958227382513769</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.715415334884362</v>
+        <v>-4.530577669108517</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.135566188197771</v>
+        <v>-4.925735595672343</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.783567911708609</v>
+        <v>-4.676690733656976</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.006345</t>
+          <t>X &lt; -0.006331</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2286637782821046</v>
+        <v>-0.2101118248869795</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.063053031556976</v>
+        <v>1.106711089957166</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.968581947102237</v>
+        <v>1.012973101642466</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8986068904903917</v>
+        <v>0.9428571428571431</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.761718738796105</v>
+        <v>1.853608001905215</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.0430093336709092</v>
+        <v>0.0263935207241488</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.629221194438578</v>
+        <v>-1.534262568501312</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.096289838225317</v>
+        <v>-2.000095328884655</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.058172895648994</v>
+        <v>-2.93706793802145</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.608792392679561</v>
+        <v>-4.560896518836437</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.514194251640447</v>
+        <v>-5.465036966372523</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-6.280616900085924</v>
+        <v>-6.206870229007635</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-6.700767753399333</v>
+        <v>-6.60202815557146</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.452983293556095</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.004539</t>
+          <t>X &lt; -0.004527</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1969416832945825</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4242847668894285</v>
+        <v>0.3724208188247928</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.1893854844525364</v>
+        <v>0.1381724636839223</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.2399417300726086</v>
+        <v>-0.2901572112098449</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.02112922842242426</v>
+        <v>0.01804181370745539</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.599961969760237</v>
+        <v>-1.623048265559746</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.404096789458066</v>
+        <v>-2.401407704067502</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.631357279767585</v>
+        <v>-2.628006014690072</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.491699947881081</v>
+        <v>-3.462426789696089</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.581426897688168</v>
+        <v>-4.525489820271844</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.745360669857227</v>
+        <v>-5.606823250264071</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.79091856866097</v>
+        <v>-5.628401329486103</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.051197319656247</v>
+        <v>-5.864069622876087</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-5.704982053122755</v>
+        <v>-5.61502476086072</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.002734</t>
+          <t>X &lt; -0.002723</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5374566728777239</v>
+        <v>0.5698357504734375</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1550942495824259</v>
+        <v>-0.09591014202187154</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6154824322377408</v>
+        <v>-0.5551789298123211</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.403892459253051</v>
+        <v>-1.342726081258199</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8923132459445426</v>
+        <v>-0.7834824305980632</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.366592759616537</v>
+        <v>-2.280028497624478</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.041854299985069</v>
+        <v>-2.930461782131722</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.377689347971291</v>
+        <v>-3.265232943563554</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.963605887696154</v>
+        <v>-3.826451948506381</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.747907886125759</v>
+        <v>-4.584749729845605</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.280693033887268</v>
+        <v>-5.11654417476047</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.311931679432199</v>
+        <v>-5.123908236871337</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.976390717137861</v>
+        <v>-4.798227369201868</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.04521858400318</v>
+        <v>-4.942367304041021</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0009283</t>
+          <t>X &lt; -0.0009186</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.6008070387087372</v>
+        <v>-0.6642920637577774</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6316116603829229</v>
+        <v>-0.6188046537996215</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.298862609170662</v>
+        <v>-1.28398672463333</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.149563896100005</v>
+        <v>-2.077012563983253</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.37995154183875</v>
+        <v>-1.263330108843967</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.499471245173694</v>
+        <v>-2.373715115886391</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.074644819698719</v>
+        <v>-2.868917647262862</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.596209376292002</v>
+        <v>-3.415312720189</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.202150660880172</v>
+        <v>-4.022331668309647</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.94307763159695</v>
+        <v>-4.76394330882556</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.638242005115991</v>
+        <v>-5.457746433184283</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.767351591180294</v>
+        <v>-5.562800588093594</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.396628281320936</v>
+        <v>-5.196261017377765</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.415707639593016</v>
+        <v>-5.273657939910827</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0008772</t>
+          <t>X &lt; 0.0008856</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2198</v>
+        <v>2204</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.1172796668979856</v>
+        <v>-0.1808490478630205</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5466475781436415</v>
+        <v>-0.4976308367728208</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.259600781080501</v>
+        <v>-1.20796764914904</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.902102910219405</v>
+        <v>-1.801738062932088</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.849483372406013</v>
+        <v>-1.769468921171701</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.324836615498192</v>
+        <v>-2.10642675994584</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.727728792946181</v>
+        <v>-2.550929235167978</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.285706527642006</v>
+        <v>-3.129093969573368</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.710325047801149</v>
+        <v>-3.595816804748559</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.105698389585555</v>
+        <v>-3.942755929267271</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.674035911482115</v>
+        <v>-4.531643136971439</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.548748668217691</v>
+        <v>-4.382732297973149</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.217793646960025</v>
+        <v>-4.097309462286525</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.059194973959883</v>
+        <v>-3.939008701904548</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.002683</t>
+          <t>X &lt; 0.00269</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2515</v>
+        <v>2518</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3760709153635773</v>
+        <v>-0.4119328858529414</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.716407127569596</v>
+        <v>-0.7282849512146541</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.031750394771016</v>
+        <v>-1.003258093923655</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.417808015281139</v>
+        <v>-1.348433435131781</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.479528863055158</v>
+        <v>-1.420649423837354</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.420439186080905</v>
+        <v>-1.324795068816272</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.021432309445565</v>
+        <v>-1.919240769056209</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.250216600571463</v>
+        <v>-2.12626503546673</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.668625286085508</v>
+        <v>-2.538892610770354</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.80369102443283</v>
+        <v>-2.667245725185644</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.206962476577061</v>
+        <v>-3.088419260933861</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.952855288653275</v>
+        <v>-2.850317409309454</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.79539178919984</v>
+        <v>-2.689478512997987</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.707288216144626</v>
+        <v>-2.639003944866658</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.004488</t>
+          <t>X &lt; 0.004494</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2807</v>
+        <v>2812</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5236206568688715</v>
+        <v>-0.5427243736285661</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7469063940608152</v>
+        <v>-0.743412979521743</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.070503401591651</v>
+        <v>-1.030805700200858</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.402911709960584</v>
+        <v>-1.342958459979741</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.265044679426389</v>
+        <v>-1.210350848751041</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.9676706497913017</v>
+        <v>-0.8830457979415769</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.265904140730065</v>
+        <v>-1.173133708011434</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.37710089839581</v>
+        <v>-1.264868056157383</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.580431809366985</v>
+        <v>-1.460336144060534</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.754194022066947</v>
+        <v>-1.625430989341062</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.136831123387644</v>
+        <v>-2.023551008320624</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.976383866767819</v>
+        <v>-1.875006786617874</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.771800324431908</v>
+        <v>-1.665612792840307</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.490888715039389</v>
+        <v>-1.416567930824939</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.006294</t>
+          <t>X &lt; 0.006298</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3051</v>
+        <v>3055</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4521202190160309</v>
+        <v>-0.4709601119995384</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6060137438927811</v>
+        <v>-0.6185743912826425</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9353186802026485</v>
+        <v>-0.9144330973787476</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.39429157262083</v>
+        <v>-1.354531891085422</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9833176232615344</v>
+        <v>-0.9449881456625207</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7186768178490297</v>
+        <v>-0.6545992944293531</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.9997865224507194</v>
+        <v>-0.9263239863386161</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.877657130230908</v>
+        <v>-0.7863698386885787</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.9386392867536841</v>
+        <v>-0.8382774836245943</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.035693925964068</v>
+        <v>-0.9249252958148517</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.451585473903975</v>
+        <v>-1.340045144324762</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.038952044926155</v>
+        <v>-0.9367131609448052</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7201803507935907</v>
+        <v>-0.6264144076172826</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.4105605519755926</v>
+        <v>-0.3446363213793333</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.008099</t>
+          <t>X &lt; 0.008103</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3282</v>
+        <v>3291</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2330423974845388</v>
+        <v>-0.2243110377238011</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4002151591496812</v>
+        <v>-0.3845392884866712</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9002473685355952</v>
+        <v>-0.8831504598354414</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.088177704989853</v>
+        <v>-1.070260094343716</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.789098501802151</v>
+        <v>-0.7857859374887184</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.353572406631308</v>
+        <v>-0.3450523719706027</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6043679784715508</v>
+        <v>-0.6015154490349701</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6149545772187253</v>
+        <v>-0.596000697401486</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6759367337415014</v>
+        <v>-0.6467766758855262</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7650521216720918</v>
+        <v>-0.7256916629942438</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.8920378486621345</v>
+        <v>-0.8523472274532722</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.7798969352977494</v>
+        <v>-0.7470159927488993</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.3911989704830106</v>
+        <v>-0.365940670759791</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1787907063829621</v>
+        <v>-0.1606101546925203</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.009905</t>
+          <t>X &lt; 0.009907</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3482</v>
+        <v>3492</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2485176332819208</v>
+        <v>-0.2419235224618745</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5564594095987516</v>
+        <v>-0.5544761246547125</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.9358998542867809</v>
+        <v>-0.9329304096335989</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.220011298021802</v>
+        <v>-1.21608060700008</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.9121298949379195</v>
+        <v>-0.9189426978948347</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6279450862764833</v>
+        <v>-0.6307493364187025</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.7545219539136525</v>
+        <v>-0.7617275584984569</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6612442391418654</v>
+        <v>-0.6689918411773874</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.6935484490056254</v>
+        <v>-0.6903993649588216</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.6959294436720285</v>
+        <v>-0.6977386240995855</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.8847441415590609</v>
+        <v>-0.8860670092909757</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.7483624872344947</v>
+        <v>-0.7548381740562817</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.5496554007365972</v>
+        <v>-0.561575822333559</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2790888882749627</v>
+        <v>-0.2965113577027125</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3648</v>
+        <v>3659</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2274333755220539</v>
+        <v>-0.2225301255405725</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4035775334342446</v>
+        <v>-0.4021965646328596</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6470265556339001</v>
+        <v>-0.6450650454965086</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7754564566183291</v>
+        <v>-0.7730600007787274</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5607842399825174</v>
+        <v>-0.5661302750849657</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5494238444617849</v>
+        <v>-0.5512448757852653</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7287858753986072</v>
+        <v>-0.7335533486431558</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.661110816839404</v>
+        <v>-0.6662617681752465</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6524274294053143</v>
+        <v>-0.661085405270363</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7754683786326524</v>
+        <v>-0.7875413454812588</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.9102476591975517</v>
+        <v>-0.922000374346311</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8333065760632721</v>
+        <v>-0.8487440339789529</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6353710330286546</v>
+        <v>-0.6550336200523361</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.4491048601402952</v>
+        <v>-0.4727154608149107</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3780</v>
+        <v>3791</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1213062229941428</v>
+        <v>-0.1178931077471361</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2946337691678025</v>
+        <v>-0.2936570404661865</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4114316724260263</v>
+        <v>-0.4102252150329733</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4516351721527201</v>
+        <v>-0.4502762430939313</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2631089392382222</v>
+        <v>-0.2674446296737329</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3472998966731922</v>
+        <v>-0.3488104803287584</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5497154938607878</v>
+        <v>-0.5531672551785078</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5006371332223765</v>
+        <v>-0.5043618550895488</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6792814546703667</v>
+        <v>-0.6850131435009104</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.7748315819745528</v>
+        <v>-0.783030906188209</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.9384845212915423</v>
+        <v>-0.9462704929935057</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.8894774793325411</v>
+        <v>-0.8999100391842703</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.5808949051477583</v>
+        <v>-0.5948551597908747</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4990561271968303</v>
+        <v>-0.5157108060857709</v>
       </c>
     </row>
     <row r="30">
@@ -5156,101 +5156,101 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3874</v>
+        <v>3885</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.07889873663827984</v>
+        <v>0.08096051990521858</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.000491212635751026</v>
+        <v>-0.0003969418621778686</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.09819911967883144</v>
+        <v>-0.09790985523639506</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1856905892756799</v>
+        <v>-0.1851274527782891</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.03681588074876174</v>
+        <v>0.03290949137619492</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1153382313475646</v>
+        <v>-0.116889294585377</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3148431730262899</v>
+        <v>-0.3177158059113907</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3813016541649645</v>
+        <v>-0.384084020737653</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6086235783502545</v>
+        <v>-0.6126463441911199</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6450813892573635</v>
+        <v>-0.6510482287875803</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.8354892376246212</v>
+        <v>-0.8409628922984567</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7868104000874752</v>
+        <v>-0.7942898328151955</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.4442660904460567</v>
+        <v>-0.4546786959728948</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3589004836854812</v>
+        <v>-0.3713874119602139</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01713</t>
+          <t>X &lt; 0.01712</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3959</v>
+        <v>3970</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.2632934357294943</v>
+        <v>0.2641789107394317</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.05043124331191251</v>
+        <v>0.05035749879693441</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.04713152943015331</v>
+        <v>0.04700977584491284</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.01046544715337205</v>
+        <v>-0.01040918880115527</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09498143697815919</v>
+        <v>0.09203474229225606</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.07273404199406031</v>
+        <v>-0.07385786188017818</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2445536221764542</v>
+        <v>-0.24653312419656</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.269141125830707</v>
+        <v>-0.2711214858263062</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4676408903843949</v>
+        <v>-0.4704012713547883</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4962771522309311</v>
+        <v>-0.5004033129984862</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6364745329313308</v>
+        <v>-0.640244618021157</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5628061835375249</v>
+        <v>-0.5680988292090419</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2618288144604008</v>
+        <v>-0.2693411749620438</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.2239211791646767</v>
+        <v>-0.2328321600548335</v>
       </c>
     </row>
     <row r="32">
@@ -5260,101 +5260,101 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4011</v>
+        <v>4022</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2526823790083981</v>
+        <v>0.2532091168726254</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.07145740908886467</v>
+        <v>0.07131198237163261</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1625546368481778</v>
+        <v>0.1621176590439006</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1571541719175613</v>
+        <v>0.1567460317460245</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2294401915921824</v>
+        <v>0.2267908349491279</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1673029940835633</v>
+        <v>0.1658476150169506</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.02821750284255131</v>
+        <v>-0.03014243943702866</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1082674618534298</v>
+        <v>-0.1100258154784939</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2800461633390015</v>
+        <v>-0.2823373693599152</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2694592862231602</v>
+        <v>-0.2728686996610818</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4602613950170067</v>
+        <v>-0.463173612335261</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3372202265621738</v>
+        <v>-0.3414626743356663</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.09538370534330198</v>
+        <v>-0.1013321575600301</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1297938207617477</v>
+        <v>-0.1366232736654922</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.02074</t>
+          <t>X &lt; 0.02073</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4055</v>
+        <v>4066</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1739512261028224</v>
+        <v>0.1743696656744262</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1985297918185864</v>
+        <v>0.1980303641111547</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.3335888625272574</v>
+        <v>0.3326934842767457</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2066972686914781</v>
+        <v>0.2061544932006143</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1985660191473144</v>
+        <v>0.1965527871812895</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.214151592946088</v>
+        <v>0.2128441834634742</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.0444613507358369</v>
+        <v>0.04287958715790552</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.03976396983045305</v>
+        <v>-0.04115623261746748</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1856945059292272</v>
+        <v>-0.1874241158647365</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1597757485409588</v>
+        <v>-0.1623707203106335</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.3507015327016916</v>
+        <v>-0.3527980870409948</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.3025412153304288</v>
+        <v>-0.3054936311708616</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.06787746666289252</v>
+        <v>-0.07222731957441653</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1241189211868701</v>
+        <v>-0.1290285468763059</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4076</v>
+        <v>4087</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.09917690172292026</v>
+        <v>0.09964427267399145</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1397961151493732</v>
+        <v>0.1394507825651203</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2721184172646005</v>
+        <v>0.2713918424916528</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2199546699879562</v>
+        <v>0.2193765472994116</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2335810539876775</v>
+        <v>0.2317330019052193</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2016525662309476</v>
+        <v>0.2005082948389258</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.03239633786227358</v>
+        <v>0.03110137873855479</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.05380149000448853</v>
+        <v>-0.05489620843510323</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1502907424838185</v>
+        <v>-0.1517306946196939</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1043614911898345</v>
+        <v>-0.1065821702663996</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2708287974390089</v>
+        <v>-0.2726164284752102</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2227198662202738</v>
+        <v>-0.2252365777481558</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.06499290570395289</v>
+        <v>-0.06856435909396907</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1197808754976322</v>
+        <v>-0.123793178557321</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.02435</t>
+          <t>X &lt; 0.02434</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4095</v>
+        <v>4105</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.02638679322416237</v>
+        <v>0.03966962241754146</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1080439684398016</v>
+        <v>0.09665522403538063</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.213564874501138</v>
+        <v>0.2262869986298313</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.2353126583776515</v>
+        <v>0.2479604235375703</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2220211464669362</v>
+        <v>0.2338219056485329</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2159871719743833</v>
+        <v>0.2282413203837663</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.02274769302518109</v>
+        <v>0.03499813188778944</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.04083277179531564</v>
+        <v>-0.02833663270368447</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1371543160938273</v>
+        <v>-0.1249024878998028</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.07097816957624303</v>
+        <v>-0.05921727814526179</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2864188920934936</v>
+        <v>-0.2740924678330927</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1895612361720751</v>
+        <v>-0.1779683541598089</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.08333489084928658</v>
+        <v>-0.07241295829917505</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.136825764966467</v>
+        <v>-0.1263085067107852</v>
       </c>
     </row>
   </sheetData>
